--- a/pitstop_produtos_categorizados_v2.xlsx
+++ b/pitstop_produtos_categorizados_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\super\Desktop\PitStop Manaira Delivery\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29E39E3-720E-4FEA-9B22-0DB4FEB53AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342A1211-DEE7-49F3-9345-7F5413B42E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="371">
   <si>
     <t>codigo_barras</t>
   </si>
@@ -231,9 +231,6 @@
     <t>CANA AGUARDENTE SERRA PRETA 350ML</t>
   </si>
   <si>
-    <t>CANETA ESFEROGRAFICA BIC</t>
-  </si>
-  <si>
     <t>CARVAO VEGETAL BRASA FORTE 10KG</t>
   </si>
   <si>
@@ -1015,12 +1012,6 @@
   </si>
   <si>
     <t>SALGADO MINEIRO DIVERSOS UN</t>
-  </si>
-  <si>
-    <t>SANTA MARIA RODO 40CM</t>
-  </si>
-  <si>
-    <t>SANTA MARIA VASSOURA MULTIUSO LONGA</t>
   </si>
   <si>
     <t>SCHWEPPES CITRUS KS 290ML</t>
@@ -1516,7 +1507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D358"/>
+  <dimension ref="A1:D355"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" style="1" bestFit="1" customWidth="1"/>
@@ -1816,7 +1807,7 @@
         <v>8.99</v>
       </c>
       <c r="D21" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1872,7 +1863,7 @@
         <v>16.989999999999998</v>
       </c>
       <c r="D25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1886,7 +1877,7 @@
         <v>16.989999999999998</v>
       </c>
       <c r="D26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1900,7 +1891,7 @@
         <v>16.989999999999998</v>
       </c>
       <c r="D27" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1914,7 +1905,7 @@
         <v>16.989999999999998</v>
       </c>
       <c r="D28" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2166,7 +2157,7 @@
         <v>22.99</v>
       </c>
       <c r="D46" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2278,7 +2269,7 @@
         <v>69.989999999999995</v>
       </c>
       <c r="D54" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -2297,13 +2288,13 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>223</v>
+        <v>40232790140</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C56">
-        <v>1.79</v>
+        <v>55.99</v>
       </c>
       <c r="D56" t="s">
         <v>31</v>
@@ -2311,13 +2302,13 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>40232790140</v>
+        <v>40232790126</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C57">
-        <v>55.99</v>
+        <v>26.99</v>
       </c>
       <c r="D57" t="s">
         <v>31</v>
@@ -2325,27 +2316,27 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>40232790126</v>
+        <v>7896045505340</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C58">
-        <v>26.99</v>
+        <v>5.49</v>
       </c>
       <c r="D58" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>7896045505340</v>
+        <v>7896045506415</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C59">
-        <v>5.49</v>
+        <v>4.49</v>
       </c>
       <c r="D59" t="s">
         <v>20</v>
@@ -2353,13 +2344,13 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>7896045506415</v>
+        <v>7891991000796</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C60">
-        <v>4.49</v>
+        <v>3.79</v>
       </c>
       <c r="D60" t="s">
         <v>20</v>
@@ -2367,13 +2358,13 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>7891991000796</v>
+        <v>7891991010023</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C61">
-        <v>3.79</v>
+        <v>3.99</v>
       </c>
       <c r="D61" t="s">
         <v>20</v>
@@ -2381,13 +2372,13 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>7891991010023</v>
+        <v>7898230716616</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C62">
-        <v>3.99</v>
+        <v>6.99</v>
       </c>
       <c r="D62" t="s">
         <v>20</v>
@@ -2395,7 +2386,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>7898230716616</v>
+        <v>7898230716654</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>71</v>
@@ -2409,7 +2400,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>7898230716654</v>
+        <v>7898230716630</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>72</v>
@@ -2423,13 +2414,13 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>7898230716630</v>
+        <v>7891991006088</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C65">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
       <c r="D65" t="s">
         <v>20</v>
@@ -2437,13 +2428,13 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>7891991006088</v>
+        <v>7891991014236</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C66">
-        <v>3.99</v>
+        <v>5.19</v>
       </c>
       <c r="D66" t="s">
         <v>20</v>
@@ -2451,13 +2442,13 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>7891991014236</v>
+        <v>7891991294942</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C67">
-        <v>5.19</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="D67" t="s">
         <v>20</v>
@@ -2465,13 +2456,13 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>7891991294942</v>
+        <v>7891149010509</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C68">
-        <v>4.1900000000000004</v>
+        <v>4.49</v>
       </c>
       <c r="D68" t="s">
         <v>20</v>
@@ -2479,13 +2470,13 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>7891149010509</v>
+        <v>7891149104932</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C69">
-        <v>4.49</v>
+        <v>3.99</v>
       </c>
       <c r="D69" t="s">
         <v>20</v>
@@ -2493,13 +2484,13 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>7891149104932</v>
+        <v>7891149101528</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C70">
-        <v>3.99</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="D70" t="s">
         <v>20</v>
@@ -2507,13 +2498,13 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>7891149101528</v>
+        <v>7891991014762</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C71">
-        <v>4.8899999999999997</v>
+        <v>4.99</v>
       </c>
       <c r="D71" t="s">
         <v>20</v>
@@ -2521,13 +2512,13 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>7891991014762</v>
+        <v>7891991298421</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C72">
-        <v>4.99</v>
+        <v>5.89</v>
       </c>
       <c r="D72" t="s">
         <v>20</v>
@@ -2535,13 +2526,13 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>7891991298421</v>
+        <v>7891991010481</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C73">
-        <v>5.89</v>
+        <v>4.59</v>
       </c>
       <c r="D73" t="s">
         <v>20</v>
@@ -2549,13 +2540,13 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>7891991010481</v>
+        <v>7891991295055</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C74">
-        <v>4.59</v>
+        <v>5.99</v>
       </c>
       <c r="D74" t="s">
         <v>20</v>
@@ -2563,13 +2554,13 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>7891991295055</v>
+        <v>7891149108718</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C75">
-        <v>5.99</v>
+        <v>7.99</v>
       </c>
       <c r="D75" t="s">
         <v>20</v>
@@ -2577,13 +2568,13 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>7891149108718</v>
+        <v>7898367984056</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C76">
-        <v>7.99</v>
+        <v>5.99</v>
       </c>
       <c r="D76" t="s">
         <v>20</v>
@@ -2591,7 +2582,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>7898367984056</v>
+        <v>7898367984070</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>85</v>
@@ -2605,13 +2596,13 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>7898367984070</v>
+        <v>7898367980010</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C78">
-        <v>5.99</v>
+        <v>5.39</v>
       </c>
       <c r="D78" t="s">
         <v>20</v>
@@ -2619,13 +2610,13 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>7898367980010</v>
+        <v>7898367983790</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C79">
-        <v>5.39</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="D79" t="s">
         <v>20</v>
@@ -2633,13 +2624,13 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>7898367983790</v>
+        <v>7898367984346</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C80">
-        <v>4.1900000000000004</v>
+        <v>5.39</v>
       </c>
       <c r="D80" t="s">
         <v>20</v>
@@ -2647,13 +2638,13 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>7898367984346</v>
+        <v>7898367984377</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C81">
-        <v>5.39</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="D81" t="s">
         <v>20</v>
@@ -2661,13 +2652,13 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>7898367984377</v>
+        <v>78936683</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>90</v>
       </c>
       <c r="C82">
-        <v>4.1900000000000004</v>
+        <v>7.19</v>
       </c>
       <c r="D82" t="s">
         <v>20</v>
@@ -2675,7 +2666,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>78936683</v>
+        <v>7896045506040</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>91</v>
@@ -2689,13 +2680,13 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>7896045506040</v>
+        <v>7896045506910</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C84">
-        <v>7.19</v>
+        <v>6.99</v>
       </c>
       <c r="D84" t="s">
         <v>20</v>
@@ -2703,13 +2694,13 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>7896045506910</v>
+        <v>7896045506873</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C85">
-        <v>6.99</v>
+        <v>5.99</v>
       </c>
       <c r="D85" t="s">
         <v>20</v>
@@ -2717,13 +2708,13 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>7896045506873</v>
+        <v>78905498</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C86">
-        <v>5.99</v>
+        <v>13.99</v>
       </c>
       <c r="D86" t="s">
         <v>20</v>
@@ -2731,13 +2722,13 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>78905498</v>
+        <v>7891991299619</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C87">
-        <v>13.99</v>
+        <v>6.99</v>
       </c>
       <c r="D87" t="s">
         <v>20</v>
@@ -2745,13 +2736,13 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>7891991299619</v>
+        <v>7891991302029</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C88">
-        <v>6.99</v>
+        <v>6.79</v>
       </c>
       <c r="D88" t="s">
         <v>20</v>
@@ -2759,13 +2750,13 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>7891991302029</v>
+        <v>7891991015493</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C89">
-        <v>6.79</v>
+        <v>4.99</v>
       </c>
       <c r="D89" t="s">
         <v>20</v>
@@ -2773,13 +2764,13 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>7891991015493</v>
+        <v>7891991297479</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C90">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
       <c r="D90" t="s">
         <v>20</v>
@@ -2787,13 +2778,13 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>7891991297479</v>
+        <v>7891991297424</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C91">
-        <v>5.99</v>
+        <v>4.99</v>
       </c>
       <c r="D91" t="s">
         <v>20</v>
@@ -2801,13 +2792,13 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>7891991297424</v>
+        <v>7891991015462</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C92">
-        <v>4.99</v>
+        <v>6.69</v>
       </c>
       <c r="D92" t="s">
         <v>20</v>
@@ -2815,13 +2806,13 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>7891991015462</v>
+        <v>7891991016223</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C93">
-        <v>6.69</v>
+        <v>5.39</v>
       </c>
       <c r="D93" t="s">
         <v>20</v>
@@ -2829,13 +2820,13 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>7891991016223</v>
+        <v>7891991295109</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C94">
-        <v>5.39</v>
+        <v>12.99</v>
       </c>
       <c r="D94" t="s">
         <v>20</v>
@@ -2843,13 +2834,13 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>7891991295109</v>
+        <v>7891991304870</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C95">
-        <v>12.99</v>
+        <v>7.99</v>
       </c>
       <c r="D95" t="s">
         <v>20</v>
@@ -2857,27 +2848,27 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>7891991304870</v>
+        <v>7891098040985</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C96">
-        <v>7.99</v>
+        <v>7.49</v>
       </c>
       <c r="D96" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>7891098040985</v>
+        <v>7891098040886</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C97">
-        <v>7.49</v>
+        <v>3.99</v>
       </c>
       <c r="D97" t="s">
         <v>31</v>
@@ -2885,231 +2876,231 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>7891098040886</v>
+        <v>7891141015267</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C98">
-        <v>3.99</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D98" t="s">
-        <v>31</v>
+        <v>178</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>7891141015267</v>
+        <v>7891000436837</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C99">
-        <v>19.989999999999998</v>
+        <v>3.49</v>
       </c>
       <c r="D99" t="s">
-        <v>179</v>
+        <v>41</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>7891000436837</v>
+        <v>8712000025649</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C100">
-        <v>3.49</v>
+        <v>119.99</v>
       </c>
       <c r="D100" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>8712000025649</v>
+        <v>3000</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>109</v>
       </c>
       <c r="C101">
-        <v>119.99</v>
+        <v>3.29</v>
       </c>
       <c r="D101" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>3000</v>
+        <v>7894900011753</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C102">
-        <v>3.29</v>
+        <v>7.99</v>
       </c>
       <c r="D102" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>7894900011753</v>
+        <v>7894900701753</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C103">
-        <v>7.99</v>
+        <v>7.49</v>
       </c>
       <c r="D103" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>7894900701753</v>
+        <v>7894900027099</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C104">
-        <v>7.49</v>
+        <v>4.79</v>
       </c>
       <c r="D104" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>7894900027099</v>
+        <v>7894900701715</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>114</v>
       </c>
       <c r="C105">
-        <v>4.79</v>
+        <v>6.49</v>
       </c>
       <c r="D105" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>7894900701715</v>
+        <v>7894900027044</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C106">
-        <v>6.49</v>
+        <v>6.99</v>
       </c>
       <c r="D106" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>7894900027044</v>
+        <v>7894900027020</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C107">
-        <v>6.99</v>
+        <v>11.79</v>
       </c>
       <c r="D107" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>7894900027020</v>
+        <v>7894900010398</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C108">
-        <v>11.79</v>
+        <v>2.79</v>
       </c>
       <c r="D108" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>7894900010398</v>
+        <v>7894900025019</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C109">
-        <v>2.79</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="D109" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>7894900025019</v>
+        <v>7894900700398</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C110">
-        <v>2.4900000000000002</v>
+        <v>2.69</v>
       </c>
       <c r="D110" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>7894900700398</v>
+        <v>78912939</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C111">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="D111" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>78912939</v>
+        <v>78909045</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C112">
-        <v>2.59</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="D112" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>78909045</v>
+        <v>7894900027082</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>122</v>
       </c>
       <c r="C113">
-        <v>2.4900000000000002</v>
+        <v>7.99</v>
       </c>
       <c r="D113" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>7894900027082</v>
+        <v>7894900014211</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>123</v>
@@ -3118,26 +3109,26 @@
         <v>7.99</v>
       </c>
       <c r="D114" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>7894900014211</v>
+        <v>3004</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>124</v>
       </c>
       <c r="C115">
-        <v>7.99</v>
+        <v>10.49</v>
       </c>
       <c r="D115" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>3004</v>
+        <v>7894900701517</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>125</v>
@@ -3146,166 +3137,166 @@
         <v>10.49</v>
       </c>
       <c r="D116" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>7894900701517</v>
+        <v>7894900027013</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C117">
-        <v>10.49</v>
+        <v>10.79</v>
       </c>
       <c r="D117" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>7894900027013</v>
+        <v>7894900010015</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C118">
-        <v>10.79</v>
+        <v>3.79</v>
       </c>
       <c r="D118" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>7894900010015</v>
+        <v>7894900700015</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C119">
-        <v>3.79</v>
+        <v>3.69</v>
       </c>
       <c r="D119" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>7894900700015</v>
+        <v>7894900013566</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C120">
-        <v>3.69</v>
+        <v>4.29</v>
       </c>
       <c r="D120" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>7894900013566</v>
+        <v>7894900703566</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C121">
-        <v>4.29</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="D121" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>7894900703566</v>
+        <v>7894900705034</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C122">
-        <v>4.1900000000000004</v>
+        <v>3.49</v>
       </c>
       <c r="D122" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>7894900705034</v>
+        <v>7898341430111</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C123">
-        <v>3.49</v>
+        <v>9.2899999999999991</v>
       </c>
       <c r="D123" t="s">
-        <v>111</v>
+        <v>370</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>7898341430111</v>
+        <v>7898341430098</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C124">
-        <v>9.2899999999999991</v>
+        <v>8.99</v>
       </c>
       <c r="D124" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>7898341430098</v>
+        <v>7898341430777</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>134</v>
       </c>
       <c r="C125">
-        <v>8.99</v>
+        <v>9.2899999999999991</v>
       </c>
       <c r="D125" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>7898341430777</v>
+        <v>7894900550061</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C126">
-        <v>9.2899999999999991</v>
+        <v>6.99</v>
       </c>
       <c r="D126" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
-        <v>7894900550061</v>
+        <v>7894900556056</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>136</v>
       </c>
       <c r="C127">
-        <v>6.99</v>
+        <v>3.79</v>
       </c>
       <c r="D127" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
-        <v>7894900556056</v>
+        <v>7894900559019</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>137</v>
@@ -3314,26 +3305,26 @@
         <v>3.79</v>
       </c>
       <c r="D128" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
-        <v>7894900559019</v>
+        <v>7894900666526</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C129">
-        <v>3.79</v>
+        <v>6.99</v>
       </c>
       <c r="D129" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
-        <v>7894900666526</v>
+        <v>7894900556063</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>139</v>
@@ -3342,26 +3333,26 @@
         <v>6.99</v>
       </c>
       <c r="D130" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
-        <v>7894900556063</v>
+        <v>7894900666502</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>140</v>
       </c>
       <c r="C131">
-        <v>6.99</v>
+        <v>3.79</v>
       </c>
       <c r="D131" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
-        <v>7894900666502</v>
+        <v>7894900550054</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>141</v>
@@ -3370,26 +3361,26 @@
         <v>3.79</v>
       </c>
       <c r="D132" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
-        <v>7894900550054</v>
+        <v>7898080664563</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>142</v>
       </c>
       <c r="C133">
-        <v>3.79</v>
+        <v>15.99</v>
       </c>
       <c r="D133" t="s">
-        <v>373</v>
+        <v>157</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
-        <v>7898080664563</v>
+        <v>7898080664389</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>143</v>
@@ -3398,12 +3389,12 @@
         <v>15.99</v>
       </c>
       <c r="D134" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
-        <v>7898080664389</v>
+        <v>7898080662668</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>144</v>
@@ -3412,12 +3403,12 @@
         <v>15.99</v>
       </c>
       <c r="D135" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
-        <v>7898080662668</v>
+        <v>7898080665409</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>145</v>
@@ -3426,26 +3417,26 @@
         <v>15.99</v>
       </c>
       <c r="D136" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
-        <v>7898080665409</v>
+        <v>7898080664396</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>146</v>
       </c>
       <c r="C137">
-        <v>15.99</v>
+        <v>7.99</v>
       </c>
       <c r="D137" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
-        <v>7898080664396</v>
+        <v>7898080664587</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>147</v>
@@ -3454,12 +3445,12 @@
         <v>7.99</v>
       </c>
       <c r="D138" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
-        <v>7898080664587</v>
+        <v>7898080665416</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>148</v>
@@ -3468,12 +3459,12 @@
         <v>7.99</v>
       </c>
       <c r="D139" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
-        <v>7898080665416</v>
+        <v>7898080665003</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>149</v>
@@ -3482,12 +3473,12 @@
         <v>7.99</v>
       </c>
       <c r="D140" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
-        <v>7898080665003</v>
+        <v>7898080664815</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>150</v>
@@ -3496,12 +3487,12 @@
         <v>7.99</v>
       </c>
       <c r="D141" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
-        <v>7898080664815</v>
+        <v>7898080664839</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>151</v>
@@ -3510,12 +3501,12 @@
         <v>7.99</v>
       </c>
       <c r="D142" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
-        <v>7898080664839</v>
+        <v>7898080664662</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>152</v>
@@ -3524,12 +3515,12 @@
         <v>7.99</v>
       </c>
       <c r="D143" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
-        <v>7898080664662</v>
+        <v>7898080665447</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>153</v>
@@ -3538,12 +3529,12 @@
         <v>7.99</v>
       </c>
       <c r="D144" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
-        <v>7898080665447</v>
+        <v>7898080664808</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>154</v>
@@ -3552,12 +3543,12 @@
         <v>7.99</v>
       </c>
       <c r="D145" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
-        <v>7898080664808</v>
+        <v>7898080663733</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>155</v>
@@ -3566,40 +3557,40 @@
         <v>7.99</v>
       </c>
       <c r="D146" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
-        <v>7898080663733</v>
+        <v>70847022305</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C147">
-        <v>7.99</v>
+        <v>10.99</v>
       </c>
       <c r="D147" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
-        <v>70847022305</v>
+        <v>70847022015</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C148">
         <v>10.99</v>
       </c>
       <c r="D148" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
-        <v>70847022015</v>
+        <v>7898938890076</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>159</v>
@@ -3608,12 +3599,12 @@
         <v>10.99</v>
       </c>
       <c r="D149" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
-        <v>7898938890076</v>
+        <v>7898938890120</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>160</v>
@@ -3622,12 +3613,12 @@
         <v>10.99</v>
       </c>
       <c r="D150" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
-        <v>7898938890120</v>
+        <v>1220000250147</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>161</v>
@@ -3636,12 +3627,12 @@
         <v>10.99</v>
       </c>
       <c r="D151" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
-        <v>1220000250147</v>
+        <v>70847034803</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>162</v>
@@ -3650,12 +3641,12 @@
         <v>10.99</v>
       </c>
       <c r="D152" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
-        <v>70847034803</v>
+        <v>70847033301</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>163</v>
@@ -3664,12 +3655,12 @@
         <v>10.99</v>
       </c>
       <c r="D153" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
-        <v>70847033301</v>
+        <v>7898938890113</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>164</v>
@@ -3678,12 +3669,12 @@
         <v>10.99</v>
       </c>
       <c r="D154" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
-        <v>7898938890113</v>
+        <v>1220000250031</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>165</v>
@@ -3692,12 +3683,12 @@
         <v>10.99</v>
       </c>
       <c r="D155" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
-        <v>1220000250031</v>
+        <v>1220000250222</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>166</v>
@@ -3706,12 +3697,12 @@
         <v>10.99</v>
       </c>
       <c r="D156" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
-        <v>1220000250222</v>
+        <v>70847022206</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>167</v>
@@ -3720,12 +3711,12 @@
         <v>10.99</v>
       </c>
       <c r="D157" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
-        <v>70847022206</v>
+        <v>7898938890090</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>168</v>
@@ -3734,12 +3725,12 @@
         <v>10.99</v>
       </c>
       <c r="D158" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
-        <v>7898938890090</v>
+        <v>70847033929</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>169</v>
@@ -3748,12 +3739,12 @@
         <v>10.99</v>
       </c>
       <c r="D159" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
-        <v>70847033929</v>
+        <v>7898947845685</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>170</v>
@@ -3762,124 +3753,124 @@
         <v>10.99</v>
       </c>
       <c r="D160" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
-        <v>7898947845685</v>
+        <v>7898947845753</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>171</v>
       </c>
       <c r="C161">
-        <v>10.99</v>
+        <v>14.99</v>
       </c>
       <c r="D161" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
-        <v>7898947845753</v>
+        <v>7899465200406</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>172</v>
       </c>
       <c r="C162">
-        <v>14.99</v>
+        <v>6.49</v>
       </c>
       <c r="D162" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
-        <v>7899465200406</v>
+        <v>7899465201854</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C163">
-        <v>6.49</v>
+        <v>18.989999999999998</v>
       </c>
       <c r="D163" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
-        <v>7899465201854</v>
+        <v>7899465200390</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C164">
-        <v>18.989999999999998</v>
+        <v>7.99</v>
       </c>
       <c r="D164" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
-        <v>7899465200390</v>
+        <v>7899465200987</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>175</v>
       </c>
       <c r="C165">
-        <v>7.99</v>
+        <v>8.49</v>
       </c>
       <c r="D165" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
-        <v>7899465200987</v>
+        <v>7899465200444</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C166">
-        <v>8.49</v>
+        <v>6.99</v>
       </c>
       <c r="D166" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
-        <v>7899465200444</v>
+        <v>7896452112582</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C167">
-        <v>6.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="D167" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
-        <v>7896452112582</v>
+        <v>7896034300802</v>
       </c>
       <c r="B168" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C168">
+        <v>18.989999999999998</v>
+      </c>
+      <c r="D168" t="s">
         <v>178</v>
-      </c>
-      <c r="C168">
-        <v>64.989999999999995</v>
-      </c>
-      <c r="D168" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
-        <v>7896034300802</v>
+        <v>7896034300239</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>180</v>
@@ -3888,26 +3879,26 @@
         <v>18.989999999999998</v>
       </c>
       <c r="D169" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
-        <v>7896034300239</v>
+        <v>7896023082979</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>181</v>
       </c>
       <c r="C170">
-        <v>18.989999999999998</v>
+        <v>49.99</v>
       </c>
       <c r="D170" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
-        <v>7896023082979</v>
+        <v>7896023082634</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>182</v>
@@ -3916,172 +3907,172 @@
         <v>49.99</v>
       </c>
       <c r="D171" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
-        <v>7896023082634</v>
+        <v>7894900030396</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>183</v>
       </c>
       <c r="C172">
-        <v>49.99</v>
+        <v>2.19</v>
       </c>
       <c r="D172" t="s">
-        <v>179</v>
+        <v>110</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
-        <v>7894900030396</v>
+        <v>3001</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C173">
-        <v>2.19</v>
+        <v>3.29</v>
       </c>
       <c r="D173" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
-        <v>3001</v>
+        <v>7894900031515</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>185</v>
       </c>
       <c r="C174">
-        <v>3.29</v>
+        <v>8.99</v>
       </c>
       <c r="D174" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
-        <v>7894900031515</v>
+        <v>7894900034219</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C175">
-        <v>8.99</v>
+        <v>7.99</v>
       </c>
       <c r="D175" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
-        <v>7894900034219</v>
+        <v>7894900030013</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>187</v>
       </c>
       <c r="C176">
-        <v>7.99</v>
+        <v>2.99</v>
       </c>
       <c r="D176" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
-        <v>7894900030013</v>
+        <v>7894900150018</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>188</v>
       </c>
       <c r="C177">
-        <v>2.99</v>
+        <v>2.79</v>
       </c>
       <c r="D177" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
-        <v>7894900150018</v>
+        <v>78912922</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>189</v>
       </c>
       <c r="C178">
-        <v>2.79</v>
+        <v>1.99</v>
       </c>
       <c r="D178" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
-        <v>78912922</v>
+        <v>7894900051513</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C179">
-        <v>1.99</v>
+        <v>8.99</v>
       </c>
       <c r="D179" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
-        <v>7894900051513</v>
+        <v>7894900050011</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>191</v>
       </c>
       <c r="C180">
-        <v>8.99</v>
+        <v>2.99</v>
       </c>
       <c r="D180" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
-        <v>7894900050011</v>
+        <v>78909052</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>192</v>
       </c>
       <c r="C181">
-        <v>2.99</v>
+        <v>1.99</v>
       </c>
       <c r="D181" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
-        <v>78909052</v>
+        <v>961</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>193</v>
       </c>
       <c r="C182">
-        <v>1.99</v>
+        <v>31.99</v>
       </c>
       <c r="D182" t="s">
-        <v>111</v>
+        <v>31</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
-        <v>961</v>
+        <v>7898399910627</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C183">
-        <v>31.99</v>
+        <v>4.49</v>
       </c>
       <c r="D183" t="s">
         <v>31</v>
@@ -4089,7 +4080,7 @@
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
-        <v>7898399910627</v>
+        <v>7898043425019</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>195</v>
@@ -4103,41 +4094,41 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
-        <v>7898043425019</v>
+        <v>5000291020706</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>196</v>
       </c>
       <c r="C185">
-        <v>4.49</v>
+        <v>129.99</v>
       </c>
       <c r="D185" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
-        <v>5000291020706</v>
+        <v>7622300847791</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>197</v>
       </c>
       <c r="C186">
-        <v>129.99</v>
+        <v>7.49</v>
       </c>
       <c r="D186" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
-        <v>7622300847791</v>
+        <v>7895800304235</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>198</v>
       </c>
       <c r="C187">
-        <v>7.49</v>
+        <v>2.99</v>
       </c>
       <c r="D187" t="s">
         <v>31</v>
@@ -4145,7 +4136,7 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
-        <v>7895800304235</v>
+        <v>7622210564313</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>199</v>
@@ -4159,7 +4150,7 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
-        <v>7622210564313</v>
+        <v>7895800304211</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>200</v>
@@ -4173,7 +4164,7 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
-        <v>7895800304211</v>
+        <v>7622210564290</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>201</v>
@@ -4187,7 +4178,7 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
-        <v>7622210564290</v>
+        <v>7895800309780</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>202</v>
@@ -4201,7 +4192,7 @@
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
-        <v>7895800309780</v>
+        <v>7895800304228</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>203</v>
@@ -4215,7 +4206,7 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
-        <v>7895800304228</v>
+        <v>7895800201503</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>204</v>
@@ -4229,7 +4220,7 @@
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
-        <v>7895800201503</v>
+        <v>7895800430002</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>205</v>
@@ -4243,35 +4234,35 @@
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
-        <v>7895800430002</v>
+        <v>7891991016124</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>206</v>
       </c>
       <c r="C195">
-        <v>2.99</v>
+        <v>1.99</v>
       </c>
       <c r="D195" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
-        <v>7891991016124</v>
+        <v>7891991002561</v>
       </c>
       <c r="B196" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C196">
-        <v>1.99</v>
+        <v>5.49</v>
       </c>
       <c r="D196" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
-        <v>7891991002561</v>
+        <v>7891991002608</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>208</v>
@@ -4280,40 +4271,40 @@
         <v>5.49</v>
       </c>
       <c r="D197" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
-        <v>7891991002608</v>
+        <v>7891991014908</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>209</v>
       </c>
       <c r="C198">
-        <v>5.49</v>
+        <v>1.99</v>
       </c>
       <c r="D198" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
-        <v>7891991014908</v>
+        <v>7891991001342</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>210</v>
       </c>
       <c r="C199">
-        <v>1.99</v>
+        <v>8.59</v>
       </c>
       <c r="D199" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
-        <v>7891991001342</v>
+        <v>7891991001373</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>211</v>
@@ -4322,26 +4313,26 @@
         <v>8.59</v>
       </c>
       <c r="D200" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
-        <v>7891991001373</v>
+        <v>7891991000826</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>212</v>
       </c>
       <c r="C201">
-        <v>8.59</v>
+        <v>2.99</v>
       </c>
       <c r="D201" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
-        <v>7891991000826</v>
+        <v>7891991000727</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>213</v>
@@ -4350,138 +4341,138 @@
         <v>2.99</v>
       </c>
       <c r="D202" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
-        <v>7891991000727</v>
+        <v>7894900911510</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>214</v>
       </c>
       <c r="C203">
-        <v>2.99</v>
+        <v>7.49</v>
       </c>
       <c r="D203" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
-        <v>7894900911510</v>
+        <v>7894900910018</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>215</v>
       </c>
       <c r="C204">
-        <v>7.49</v>
+        <v>2.79</v>
       </c>
       <c r="D204" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
-        <v>7894900910018</v>
+        <v>7894900920017</v>
       </c>
       <c r="B205" s="2" t="s">
         <v>216</v>
       </c>
       <c r="C205">
-        <v>2.79</v>
+        <v>2.59</v>
       </c>
       <c r="D205" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
-        <v>7894900920017</v>
+        <v>7894900921519</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>217</v>
       </c>
       <c r="C206">
-        <v>2.59</v>
+        <v>7.49</v>
       </c>
       <c r="D206" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
-        <v>7894900921519</v>
+        <v>7892840812850</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>218</v>
       </c>
       <c r="C207">
-        <v>7.49</v>
+        <v>4.79</v>
       </c>
       <c r="D207" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
-        <v>7892840812850</v>
+        <v>7892840812416</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>219</v>
       </c>
       <c r="C208">
-        <v>4.79</v>
+        <v>8.69</v>
       </c>
       <c r="D208" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
-        <v>7892840812416</v>
+        <v>7892840812423</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>220</v>
       </c>
       <c r="C209">
-        <v>8.69</v>
+        <v>4.79</v>
       </c>
       <c r="D209" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
-        <v>7892840812423</v>
+        <v>7892840812874</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>221</v>
       </c>
       <c r="C210">
-        <v>4.79</v>
+        <v>8.49</v>
       </c>
       <c r="D210" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
-        <v>7892840812874</v>
+        <v>78938793</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>222</v>
       </c>
       <c r="C211">
-        <v>8.49</v>
+        <v>1.99</v>
       </c>
       <c r="D211" t="s">
-        <v>111</v>
+        <v>31</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
-        <v>78938793</v>
+        <v>78938816</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>223</v>
@@ -4495,7 +4486,7 @@
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
-        <v>78938816</v>
+        <v>78938854</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>224</v>
@@ -4509,7 +4500,7 @@
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
-        <v>78938854</v>
+        <v>78938830</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>225</v>
@@ -4523,7 +4514,7 @@
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
-        <v>78938830</v>
+        <v>78938878</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>226</v>
@@ -4537,7 +4528,7 @@
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
-        <v>78938878</v>
+        <v>78938823</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>227</v>
@@ -4551,7 +4542,7 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
-        <v>78938823</v>
+        <v>78938847</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>228</v>
@@ -4565,7 +4556,7 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
-        <v>78938847</v>
+        <v>78938861</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>229</v>
@@ -4579,77 +4570,77 @@
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
-        <v>78938861</v>
+        <v>7898906925021</v>
       </c>
       <c r="B219" s="2" t="s">
         <v>230</v>
       </c>
       <c r="C219">
-        <v>1.99</v>
+        <v>29.99</v>
       </c>
       <c r="D219" t="s">
-        <v>31</v>
+        <v>369</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
-        <v>7898906925021</v>
+        <v>7898906925281</v>
       </c>
       <c r="B220" s="2" t="s">
         <v>231</v>
       </c>
       <c r="C220">
-        <v>29.99</v>
+        <v>47.99</v>
       </c>
       <c r="D220" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
-        <v>7898906925281</v>
+        <v>7898906925038</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>232</v>
       </c>
       <c r="C221">
-        <v>47.99</v>
+        <v>39.99</v>
       </c>
       <c r="D221" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
-        <v>7898906925038</v>
+        <v>7898906925076</v>
       </c>
       <c r="B222" s="2" t="s">
         <v>233</v>
       </c>
       <c r="C222">
-        <v>39.99</v>
+        <v>7.99</v>
       </c>
       <c r="D222" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
-        <v>7898906925076</v>
+        <v>7898906925236</v>
       </c>
       <c r="B223" s="2" t="s">
         <v>234</v>
       </c>
       <c r="C223">
-        <v>7.99</v>
+        <v>16.989999999999998</v>
       </c>
       <c r="D223" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
-        <v>7898906925236</v>
+        <v>7898906925557</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>235</v>
@@ -4658,12 +4649,12 @@
         <v>16.989999999999998</v>
       </c>
       <c r="D224" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
-        <v>7898906925557</v>
+        <v>7898906925472</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>236</v>
@@ -4672,40 +4663,40 @@
         <v>16.989999999999998</v>
       </c>
       <c r="D225" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
-        <v>7898906925472</v>
+        <v>7898906925212</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>237</v>
       </c>
       <c r="C226">
-        <v>16.989999999999998</v>
+        <v>11.99</v>
       </c>
       <c r="D226" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
-        <v>7898906925212</v>
+        <v>7898906925519</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>238</v>
       </c>
       <c r="C227">
-        <v>11.99</v>
+        <v>16.989999999999998</v>
       </c>
       <c r="D227" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
-        <v>7898906925519</v>
+        <v>7898906925274</v>
       </c>
       <c r="B228" s="2" t="s">
         <v>239</v>
@@ -4714,12 +4705,12 @@
         <v>16.989999999999998</v>
       </c>
       <c r="D228" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
-        <v>7898906925274</v>
+        <v>7898906925229</v>
       </c>
       <c r="B229" s="2" t="s">
         <v>240</v>
@@ -4728,26 +4719,26 @@
         <v>16.989999999999998</v>
       </c>
       <c r="D229" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
-        <v>7898906925229</v>
+        <v>7898906925618</v>
       </c>
       <c r="B230" s="2" t="s">
         <v>241</v>
       </c>
       <c r="C230">
-        <v>16.989999999999998</v>
+        <v>12.99</v>
       </c>
       <c r="D230" t="s">
-        <v>372</v>
+        <v>54</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
-        <v>7898906925618</v>
+        <v>7898906925656</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>242</v>
@@ -4761,7 +4752,7 @@
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
-        <v>7898906925656</v>
+        <v>7898906925632</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>243</v>
@@ -4770,12 +4761,12 @@
         <v>12.99</v>
       </c>
       <c r="D232" t="s">
-        <v>54</v>
+        <v>369</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
-        <v>7898906925632</v>
+        <v>7898906925601</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>244</v>
@@ -4784,26 +4775,26 @@
         <v>12.99</v>
       </c>
       <c r="D233" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
-        <v>7898906925601</v>
+        <v>80878018</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>245</v>
       </c>
       <c r="C234">
-        <v>12.99</v>
+        <v>3.49</v>
       </c>
       <c r="D234" t="s">
-        <v>372</v>
+        <v>31</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
-        <v>80878018</v>
+        <v>80935513</v>
       </c>
       <c r="B235" s="2" t="s">
         <v>246</v>
@@ -4817,13 +4808,13 @@
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
-        <v>80935513</v>
+        <v>7895144603063</v>
       </c>
       <c r="B236" s="2" t="s">
         <v>247</v>
       </c>
       <c r="C236">
-        <v>3.49</v>
+        <v>2.99</v>
       </c>
       <c r="D236" t="s">
         <v>31</v>
@@ -4831,7 +4822,7 @@
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
-        <v>7895144603063</v>
+        <v>7896262304306</v>
       </c>
       <c r="B237" s="2" t="s">
         <v>248</v>
@@ -4845,7 +4836,7 @@
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
-        <v>7896262304306</v>
+        <v>7895144603148</v>
       </c>
       <c r="B238" s="2" t="s">
         <v>249</v>
@@ -4859,7 +4850,7 @@
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
-        <v>7895144603148</v>
+        <v>7895144603223</v>
       </c>
       <c r="B239" s="2" t="s">
         <v>250</v>
@@ -4873,7 +4864,7 @@
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
-        <v>7895144603223</v>
+        <v>7895144603087</v>
       </c>
       <c r="B240" s="2" t="s">
         <v>251</v>
@@ -4887,13 +4878,13 @@
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
-        <v>7895144603087</v>
+        <v>7895144297590</v>
       </c>
       <c r="B241" s="2" t="s">
         <v>252</v>
       </c>
       <c r="C241">
-        <v>2.99</v>
+        <v>12.99</v>
       </c>
       <c r="D241" t="s">
         <v>31</v>
@@ -4901,7 +4892,7 @@
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
-        <v>7895144297590</v>
+        <v>78922327</v>
       </c>
       <c r="B242" s="2" t="s">
         <v>253</v>
@@ -4915,7 +4906,7 @@
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
-        <v>78922327</v>
+        <v>7895144295664</v>
       </c>
       <c r="B243" s="2" t="s">
         <v>254</v>
@@ -4929,7 +4920,7 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
-        <v>7895144295664</v>
+        <v>78922310</v>
       </c>
       <c r="B244" s="2" t="s">
         <v>255</v>
@@ -4943,7 +4934,7 @@
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
-        <v>78922310</v>
+        <v>7895144899978</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>256</v>
@@ -4957,7 +4948,7 @@
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
-        <v>7895144899978</v>
+        <v>78922334</v>
       </c>
       <c r="B246" s="2" t="s">
         <v>257</v>
@@ -4971,7 +4962,7 @@
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
-        <v>78922334</v>
+        <v>7895144293080</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>258</v>
@@ -4985,13 +4976,13 @@
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
-        <v>7895144293080</v>
+        <v>7895144899930</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>259</v>
       </c>
       <c r="C248">
-        <v>12.99</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="D248" t="s">
         <v>31</v>
@@ -4999,27 +4990,27 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
-        <v>7895144899930</v>
+        <v>7892840822613</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>260</v>
       </c>
       <c r="C249">
-        <v>2.4900000000000002</v>
+        <v>10.99</v>
       </c>
       <c r="D249" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
-        <v>7892840822613</v>
+        <v>7898918339229</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>261</v>
       </c>
       <c r="C250">
-        <v>10.99</v>
+        <v>2.99</v>
       </c>
       <c r="D250" t="s">
         <v>27</v>
@@ -5027,119 +5018,119 @@
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
-        <v>7898918339229</v>
+        <v>7892840800406</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>262</v>
       </c>
       <c r="C251">
-        <v>2.99</v>
+        <v>5.19</v>
       </c>
       <c r="D251" t="s">
-        <v>27</v>
+        <v>110</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
-        <v>7892840800406</v>
+        <v>7892840800000</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>263</v>
       </c>
       <c r="C252">
-        <v>5.19</v>
+        <v>7.99</v>
       </c>
       <c r="D252" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
-        <v>7892840800000</v>
+        <v>7892840800079</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>264</v>
       </c>
       <c r="C253">
-        <v>7.99</v>
+        <v>2.99</v>
       </c>
       <c r="D253" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
-        <v>7892840800079</v>
+        <v>7892840820862</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>265</v>
       </c>
       <c r="C254">
-        <v>2.99</v>
+        <v>5.19</v>
       </c>
       <c r="D254" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
-        <v>7892840820862</v>
+        <v>7892840800567</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>266</v>
       </c>
       <c r="C255">
-        <v>5.19</v>
+        <v>1.99</v>
       </c>
       <c r="D255" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
-        <v>7892840800567</v>
+        <v>7892840813444</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>267</v>
       </c>
       <c r="C256">
-        <v>1.99</v>
+        <v>8.39</v>
       </c>
       <c r="D256" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
-        <v>7892840813444</v>
+        <v>7892840813505</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>268</v>
       </c>
       <c r="C257">
-        <v>8.39</v>
+        <v>2.99</v>
       </c>
       <c r="D257" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
-        <v>7892840813505</v>
+        <v>7898339040421</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>269</v>
       </c>
       <c r="C258">
-        <v>2.99</v>
+        <v>6.99</v>
       </c>
       <c r="D258" t="s">
-        <v>111</v>
+        <v>31</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
-        <v>7898339040421</v>
+        <v>7898339041459</v>
       </c>
       <c r="B259" s="2" t="s">
         <v>270</v>
@@ -5153,7 +5144,7 @@
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
-        <v>7898339041459</v>
+        <v>7898339040407</v>
       </c>
       <c r="B260" s="2" t="s">
         <v>271</v>
@@ -5167,35 +5158,35 @@
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
-        <v>7898339040407</v>
+        <v>7891075020023</v>
       </c>
       <c r="B261" s="2" t="s">
         <v>272</v>
       </c>
       <c r="C261">
-        <v>6.99</v>
+        <v>8.99</v>
       </c>
       <c r="D261" t="s">
-        <v>31</v>
+        <v>273</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
-        <v>7891075020023</v>
+        <v>7891150094321</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C262">
         <v>8.99</v>
       </c>
       <c r="D262" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
-        <v>7891150094321</v>
+        <v>7891075010130</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>275</v>
@@ -5204,26 +5195,26 @@
         <v>8.99</v>
       </c>
       <c r="D263" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
-        <v>7891075010130</v>
+        <v>7891150064904</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>276</v>
       </c>
       <c r="C264">
-        <v>8.99</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D264" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
-        <v>7891150064904</v>
+        <v>7891150023093</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>277</v>
@@ -5232,12 +5223,12 @@
         <v>19.989999999999998</v>
       </c>
       <c r="D265" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
-        <v>7891150023093</v>
+        <v>7891075403215</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>278</v>
@@ -5246,12 +5237,12 @@
         <v>19.989999999999998</v>
       </c>
       <c r="D266" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
-        <v>7891075403215</v>
+        <v>7891150041042</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>279</v>
@@ -5260,12 +5251,12 @@
         <v>19.989999999999998</v>
       </c>
       <c r="D267" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
-        <v>7891150041042</v>
+        <v>7891150081963</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>280</v>
@@ -5274,26 +5265,26 @@
         <v>19.989999999999998</v>
       </c>
       <c r="D268" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
-        <v>7891150081963</v>
+        <v>7891150099937</v>
       </c>
       <c r="B269" s="2" t="s">
         <v>281</v>
       </c>
       <c r="C269">
-        <v>19.989999999999998</v>
+        <v>10.99</v>
       </c>
       <c r="D269" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
-        <v>7891150099937</v>
+        <v>7891075060210</v>
       </c>
       <c r="B270" s="2" t="s">
         <v>282</v>
@@ -5302,12 +5293,12 @@
         <v>10.99</v>
       </c>
       <c r="D270" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
-        <v>7891075060210</v>
+        <v>7891150089051</v>
       </c>
       <c r="B271" s="2" t="s">
         <v>283</v>
@@ -5316,82 +5307,82 @@
         <v>10.99</v>
       </c>
       <c r="D271" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
-        <v>7891150089051</v>
+        <v>7897326802011</v>
       </c>
       <c r="B272" s="2" t="s">
         <v>284</v>
       </c>
       <c r="C272">
-        <v>10.99</v>
+        <v>13.99</v>
       </c>
       <c r="D272" t="s">
-        <v>274</v>
+        <v>31</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
-        <v>7897326802011</v>
+        <v>7894900503029</v>
       </c>
       <c r="B273" s="2" t="s">
         <v>285</v>
       </c>
       <c r="C273">
-        <v>13.99</v>
+        <v>5.49</v>
       </c>
       <c r="D273" t="s">
-        <v>31</v>
+        <v>286</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
-        <v>7894900503029</v>
+        <v>7894900501001</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C274">
         <v>5.49</v>
       </c>
       <c r="D274" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
-        <v>7894900501001</v>
+        <v>7898275016023</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>288</v>
       </c>
       <c r="C275">
-        <v>5.49</v>
+        <v>8.99</v>
       </c>
       <c r="D275" t="s">
-        <v>287</v>
+        <v>31</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
-        <v>7898275016023</v>
+        <v>9002490229160</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>289</v>
       </c>
       <c r="C276">
-        <v>8.99</v>
+        <v>9.99</v>
       </c>
       <c r="D276" t="s">
-        <v>31</v>
+        <v>157</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
-        <v>9002490229160</v>
+        <v>9002490275013</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>290</v>
@@ -5400,12 +5391,12 @@
         <v>9.99</v>
       </c>
       <c r="D277" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
-        <v>9002490275013</v>
+        <v>9002490247379</v>
       </c>
       <c r="B278" s="2" t="s">
         <v>291</v>
@@ -5414,12 +5405,12 @@
         <v>9.99</v>
       </c>
       <c r="D278" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
-        <v>9002490247379</v>
+        <v>9002490258825</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>292</v>
@@ -5428,12 +5419,12 @@
         <v>9.99</v>
       </c>
       <c r="D279" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
-        <v>9002490258825</v>
+        <v>611269101713</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>293</v>
@@ -5442,12 +5433,12 @@
         <v>9.99</v>
       </c>
       <c r="D280" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
-        <v>611269101713</v>
+        <v>9002490283063</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>294</v>
@@ -5456,12 +5447,12 @@
         <v>9.99</v>
       </c>
       <c r="D281" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
-        <v>9002490283063</v>
+        <v>611269991000</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>295</v>
@@ -5470,26 +5461,26 @@
         <v>9.99</v>
       </c>
       <c r="D282" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
-        <v>611269991000</v>
+        <v>9002490243678</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>296</v>
       </c>
       <c r="C283">
-        <v>9.99</v>
+        <v>13.99</v>
       </c>
       <c r="D283" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
-        <v>9002490243678</v>
+        <v>9002490209346</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>297</v>
@@ -5498,82 +5489,82 @@
         <v>13.99</v>
       </c>
       <c r="D284" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
-        <v>9002490209346</v>
+        <v>9002490214166</v>
       </c>
       <c r="B285" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C285">
-        <v>13.99</v>
+        <v>17.989999999999998</v>
       </c>
       <c r="D285" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
-        <v>9002490214166</v>
+        <v>7891149441204</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>299</v>
       </c>
       <c r="C286">
-        <v>17.989999999999998</v>
+        <v>5.19</v>
       </c>
       <c r="D286" t="s">
-        <v>158</v>
+        <v>110</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
-        <v>7891149441204</v>
+        <v>7891149440801</v>
       </c>
       <c r="B287" s="2" t="s">
         <v>300</v>
       </c>
       <c r="C287">
-        <v>5.19</v>
+        <v>6.69</v>
       </c>
       <c r="D287" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
-        <v>7891149440801</v>
+        <v>1220000250055</v>
       </c>
       <c r="B288" s="2" t="s">
         <v>301</v>
       </c>
       <c r="C288">
-        <v>6.69</v>
+        <v>10.99</v>
       </c>
       <c r="D288" t="s">
-        <v>111</v>
+        <v>157</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
-        <v>1220000250055</v>
+        <v>7892840808020</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>302</v>
       </c>
       <c r="C289">
-        <v>10.99</v>
+        <v>5.99</v>
       </c>
       <c r="D289" t="s">
-        <v>158</v>
+        <v>286</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
-        <v>7892840808020</v>
+        <v>7892840808037</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>303</v>
@@ -5582,12 +5573,12 @@
         <v>5.99</v>
       </c>
       <c r="D290" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
-        <v>7892840808037</v>
+        <v>7892840808174</v>
       </c>
       <c r="B291" s="2" t="s">
         <v>304</v>
@@ -5596,12 +5587,12 @@
         <v>5.99</v>
       </c>
       <c r="D291" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
-        <v>7892840808174</v>
+        <v>7892840808044</v>
       </c>
       <c r="B292" s="2" t="s">
         <v>305</v>
@@ -5610,12 +5601,12 @@
         <v>5.99</v>
       </c>
       <c r="D292" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
-        <v>7892840808044</v>
+        <v>7892840808051</v>
       </c>
       <c r="B293" s="2" t="s">
         <v>306</v>
@@ -5624,46 +5615,46 @@
         <v>5.99</v>
       </c>
       <c r="D293" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
-        <v>7892840808051</v>
+        <v>7891050004406</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>307</v>
       </c>
       <c r="C294">
-        <v>5.99</v>
+        <v>29.99</v>
       </c>
       <c r="D294" t="s">
-        <v>287</v>
+        <v>54</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
-        <v>7891050004406</v>
+        <v>7892840822309</v>
       </c>
       <c r="B295" s="2" t="s">
         <v>308</v>
       </c>
       <c r="C295">
-        <v>29.99</v>
+        <v>3.69</v>
       </c>
       <c r="D295" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
-        <v>7892840822309</v>
+        <v>7892840822859</v>
       </c>
       <c r="B296" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C296">
-        <v>3.69</v>
+        <v>1.99</v>
       </c>
       <c r="D296" t="s">
         <v>27</v>
@@ -5671,13 +5662,13 @@
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
-        <v>7892840822859</v>
+        <v>7892840823061</v>
       </c>
       <c r="B297" s="2" t="s">
         <v>310</v>
       </c>
       <c r="C297">
-        <v>1.99</v>
+        <v>3.49</v>
       </c>
       <c r="D297" t="s">
         <v>27</v>
@@ -5685,7 +5676,7 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
-        <v>7892840823061</v>
+        <v>7892840823504</v>
       </c>
       <c r="B298" s="2" t="s">
         <v>311</v>
@@ -5699,13 +5690,13 @@
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
-        <v>7892840823504</v>
+        <v>7891091061789</v>
       </c>
       <c r="B299" s="2" t="s">
         <v>312</v>
       </c>
       <c r="C299">
-        <v>3.49</v>
+        <v>9.99</v>
       </c>
       <c r="D299" t="s">
         <v>27</v>
@@ -5713,13 +5704,13 @@
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
-        <v>7891091061789</v>
+        <v>7891091061680</v>
       </c>
       <c r="B300" s="2" t="s">
         <v>313</v>
       </c>
       <c r="C300">
-        <v>9.99</v>
+        <v>3.99</v>
       </c>
       <c r="D300" t="s">
         <v>27</v>
@@ -5727,7 +5718,7 @@
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
-        <v>7891091061680</v>
+        <v>7891091061697</v>
       </c>
       <c r="B301" s="2" t="s">
         <v>314</v>
@@ -5741,7 +5732,7 @@
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
-        <v>7891091061697</v>
+        <v>7891091061932</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>315</v>
@@ -5755,7 +5746,7 @@
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
-        <v>7891091061932</v>
+        <v>7891091061628</v>
       </c>
       <c r="B303" s="2" t="s">
         <v>316</v>
@@ -5769,7 +5760,7 @@
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
-        <v>7891091061628</v>
+        <v>7891091061710</v>
       </c>
       <c r="B304" s="2" t="s">
         <v>317</v>
@@ -5783,7 +5774,7 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
-        <v>7891091061710</v>
+        <v>7891091061659</v>
       </c>
       <c r="B305" s="2" t="s">
         <v>318</v>
@@ -5797,7 +5788,7 @@
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
-        <v>7891091061659</v>
+        <v>7891091061291</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>319</v>
@@ -5811,13 +5802,13 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
-        <v>7891091061291</v>
+        <v>7892840822477</v>
       </c>
       <c r="B307" s="2" t="s">
         <v>320</v>
       </c>
       <c r="C307">
-        <v>3.99</v>
+        <v>1.99</v>
       </c>
       <c r="D307" t="s">
         <v>27</v>
@@ -5825,7 +5816,7 @@
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
-        <v>7892840822477</v>
+        <v>7892840822521</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>321</v>
@@ -5839,13 +5830,13 @@
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
-        <v>7892840822521</v>
+        <v>7892840822637</v>
       </c>
       <c r="B309" s="2" t="s">
         <v>322</v>
       </c>
       <c r="C309">
-        <v>1.99</v>
+        <v>2.99</v>
       </c>
       <c r="D309" t="s">
         <v>27</v>
@@ -5853,7 +5844,7 @@
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
-        <v>7892840822637</v>
+        <v>7892840822644</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>323</v>
@@ -5867,13 +5858,13 @@
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
-        <v>7892840822644</v>
+        <v>782</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>324</v>
       </c>
       <c r="C311">
-        <v>2.99</v>
+        <v>7.99</v>
       </c>
       <c r="D311" t="s">
         <v>27</v>
@@ -5881,77 +5872,77 @@
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
-        <v>782</v>
+        <v>7894900325362</v>
       </c>
       <c r="B312" s="2" t="s">
         <v>325</v>
       </c>
       <c r="C312">
-        <v>7.99</v>
+        <v>3.29</v>
       </c>
       <c r="D312" t="s">
-        <v>27</v>
+        <v>110</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
-        <v>7896314703521</v>
+        <v>7894900184075</v>
       </c>
       <c r="B313" s="2" t="s">
         <v>326</v>
       </c>
       <c r="C313">
-        <v>23.99</v>
+        <v>5.99</v>
       </c>
       <c r="D313" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
-        <v>7896314703064</v>
+        <v>7891149840878</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>327</v>
       </c>
       <c r="C314">
-        <v>18.989999999999998</v>
+        <v>6.69</v>
       </c>
       <c r="D314" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
-        <v>7894900325362</v>
+        <v>7891991301114</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>328</v>
       </c>
       <c r="C315">
-        <v>3.29</v>
+        <v>8.19</v>
       </c>
       <c r="D315" t="s">
-        <v>111</v>
+        <v>20</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
-        <v>7894900184075</v>
+        <v>7891991301138</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>329</v>
       </c>
       <c r="C316">
-        <v>5.99</v>
+        <v>8.19</v>
       </c>
       <c r="D316" t="s">
-        <v>111</v>
+        <v>20</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
-        <v>7891149840878</v>
+        <v>7891149105564</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>330</v>
@@ -5965,13 +5956,13 @@
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
-        <v>7891991301114</v>
+        <v>7891991306164</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>331</v>
       </c>
       <c r="C318">
-        <v>8.19</v>
+        <v>6.69</v>
       </c>
       <c r="D318" t="s">
         <v>20</v>
@@ -5979,13 +5970,13 @@
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
-        <v>7891991301138</v>
+        <v>7891149200504</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>332</v>
       </c>
       <c r="C319">
-        <v>8.19</v>
+        <v>4.29</v>
       </c>
       <c r="D319" t="s">
         <v>20</v>
@@ -5993,13 +5984,13 @@
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
-        <v>7891149105564</v>
+        <v>7891149201006</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>333</v>
       </c>
       <c r="C320">
-        <v>6.69</v>
+        <v>5.79</v>
       </c>
       <c r="D320" t="s">
         <v>20</v>
@@ -6007,77 +5998,77 @@
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
-        <v>7891991306164</v>
+        <v>7891991001359</v>
       </c>
       <c r="B321" s="2" t="s">
         <v>334</v>
       </c>
       <c r="C321">
-        <v>6.69</v>
+        <v>8.59</v>
       </c>
       <c r="D321" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
-        <v>7891149200504</v>
+        <v>7891991002578</v>
       </c>
       <c r="B322" s="2" t="s">
         <v>335</v>
       </c>
       <c r="C322">
-        <v>4.29</v>
+        <v>5.19</v>
       </c>
       <c r="D322" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
-        <v>7891149201006</v>
+        <v>7891150077263</v>
       </c>
       <c r="B323" s="2" t="s">
         <v>336</v>
       </c>
       <c r="C323">
-        <v>5.79</v>
+        <v>27.99</v>
       </c>
       <c r="D323" t="s">
-        <v>20</v>
+        <v>273</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
-        <v>7891991001359</v>
+        <v>7891150050235</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>337</v>
       </c>
       <c r="C324">
-        <v>8.59</v>
+        <v>27.99</v>
       </c>
       <c r="D324" t="s">
-        <v>111</v>
+        <v>273</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
-        <v>7891991002578</v>
+        <v>7891150050242</v>
       </c>
       <c r="B325" s="2" t="s">
         <v>338</v>
       </c>
       <c r="C325">
-        <v>5.19</v>
+        <v>27.99</v>
       </c>
       <c r="D325" t="s">
-        <v>111</v>
+        <v>273</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" s="1">
-        <v>7891150077263</v>
+        <v>7891150055858</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>339</v>
@@ -6086,172 +6077,172 @@
         <v>27.99</v>
       </c>
       <c r="D326" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
-        <v>7891150050235</v>
+        <v>7894900681260</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>340</v>
       </c>
       <c r="C327">
-        <v>27.99</v>
+        <v>5.79</v>
       </c>
       <c r="D327" t="s">
-        <v>274</v>
+        <v>110</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
-        <v>7891150050242</v>
+        <v>3003</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>341</v>
       </c>
       <c r="C328">
-        <v>27.99</v>
+        <v>3.29</v>
       </c>
       <c r="D328" t="s">
-        <v>274</v>
+        <v>110</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
-        <v>7891150055858</v>
+        <v>7894900061512</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>342</v>
       </c>
       <c r="C329">
-        <v>27.99</v>
+        <v>8.49</v>
       </c>
       <c r="D329" t="s">
-        <v>274</v>
+        <v>110</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
-        <v>7894900681260</v>
+        <v>7894900681017</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>343</v>
       </c>
       <c r="C330">
-        <v>5.79</v>
+        <v>2.99</v>
       </c>
       <c r="D330" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" s="1">
-        <v>3003</v>
+        <v>7894900060010</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>344</v>
       </c>
       <c r="C331">
-        <v>3.29</v>
+        <v>2.79</v>
       </c>
       <c r="D331" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
-        <v>7894900061512</v>
+        <v>7894900681000</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>345</v>
       </c>
       <c r="C332">
-        <v>8.49</v>
+        <v>8.99</v>
       </c>
       <c r="D332" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
-        <v>7894900681017</v>
+        <v>7894900681178</v>
       </c>
       <c r="B333" s="2" t="s">
         <v>346</v>
       </c>
       <c r="C333">
-        <v>2.99</v>
+        <v>2.19</v>
       </c>
       <c r="D333" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
-        <v>7894900060010</v>
+        <v>78939738</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>347</v>
       </c>
       <c r="C334">
-        <v>2.79</v>
+        <v>1.99</v>
       </c>
       <c r="D334" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
-        <v>7894900681000</v>
+        <v>7898942775314</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>348</v>
       </c>
       <c r="C335">
-        <v>8.99</v>
+        <v>15.99</v>
       </c>
       <c r="D335" t="s">
-        <v>111</v>
+        <v>31</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
-        <v>7894900681178</v>
+        <v>7896945400813</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>349</v>
       </c>
       <c r="C336">
-        <v>2.19</v>
+        <v>7.99</v>
       </c>
       <c r="D336" t="s">
-        <v>111</v>
+        <v>31</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
-        <v>78939738</v>
+        <v>78945494</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>350</v>
       </c>
       <c r="C337">
-        <v>1.99</v>
+        <v>2.99</v>
       </c>
       <c r="D337" t="s">
-        <v>111</v>
+        <v>31</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
-        <v>7898942775314</v>
+        <v>7894321722016</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>351</v>
       </c>
       <c r="C338">
-        <v>15.99</v>
+        <v>2.69</v>
       </c>
       <c r="D338" t="s">
         <v>31</v>
@@ -6259,13 +6250,13 @@
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
-        <v>7896945400813</v>
+        <v>7891137000055</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C339">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
       <c r="D339" t="s">
         <v>31</v>
@@ -6273,13 +6264,13 @@
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
-        <v>78945494</v>
+        <v>7891137006637</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>353</v>
       </c>
       <c r="C340">
-        <v>2.99</v>
+        <v>14.99</v>
       </c>
       <c r="D340" t="s">
         <v>31</v>
@@ -6287,13 +6278,13 @@
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
-        <v>7894321722016</v>
+        <v>7891137006620</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>354</v>
       </c>
       <c r="C341">
-        <v>2.69</v>
+        <v>7.99</v>
       </c>
       <c r="D341" t="s">
         <v>31</v>
@@ -6301,13 +6292,13 @@
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
-        <v>7891137000055</v>
+        <v>7891137000017</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>355</v>
       </c>
       <c r="C342">
-        <v>6.99</v>
+        <v>14.99</v>
       </c>
       <c r="D342" t="s">
         <v>31</v>
@@ -6315,13 +6306,13 @@
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
-        <v>7891137006637</v>
+        <v>78915398</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>356</v>
       </c>
       <c r="C343">
-        <v>14.99</v>
+        <v>7.99</v>
       </c>
       <c r="D343" t="s">
         <v>31</v>
@@ -6329,83 +6320,83 @@
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
-        <v>7891137006620</v>
+        <v>5604424244108</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>357</v>
       </c>
       <c r="C344">
-        <v>7.99</v>
+        <v>54.99</v>
       </c>
       <c r="D344" t="s">
-        <v>31</v>
+        <v>178</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
-        <v>7891137000017</v>
+        <v>7896037913146</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>358</v>
       </c>
       <c r="C345">
-        <v>14.99</v>
+        <v>16.989999999999998</v>
       </c>
       <c r="D345" t="s">
-        <v>31</v>
+        <v>178</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" s="1">
-        <v>78915398</v>
+        <v>7312040017034</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>359</v>
       </c>
       <c r="C346">
-        <v>7.99</v>
+        <v>109.99</v>
       </c>
       <c r="D346" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" s="1">
-        <v>5604424244108</v>
+        <v>7891050000903</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>360</v>
       </c>
       <c r="C347">
-        <v>54.99</v>
+        <v>37.99</v>
       </c>
       <c r="D347" t="s">
-        <v>179</v>
+        <v>54</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" s="1">
-        <v>7896037913146</v>
+        <v>7898012860537</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>361</v>
       </c>
       <c r="C348">
-        <v>16.989999999999998</v>
+        <v>17.989999999999998</v>
       </c>
       <c r="D348" t="s">
-        <v>179</v>
+        <v>54</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
-        <v>7312040017034</v>
+        <v>7893218003610</v>
       </c>
       <c r="B349" s="2" t="s">
         <v>362</v>
       </c>
       <c r="C349">
-        <v>109.99</v>
+        <v>5.99</v>
       </c>
       <c r="D349" t="s">
         <v>54</v>
@@ -6413,27 +6404,27 @@
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
-        <v>7891050000903</v>
+        <v>7893218003603</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>363</v>
       </c>
       <c r="C350">
-        <v>37.99</v>
+        <v>6.99</v>
       </c>
       <c r="D350" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" s="1">
-        <v>7898012860537</v>
+        <v>7893218000473</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>364</v>
       </c>
       <c r="C351">
-        <v>17.989999999999998</v>
+        <v>39.99</v>
       </c>
       <c r="D351" t="s">
         <v>54</v>
@@ -6441,13 +6432,13 @@
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" s="1">
-        <v>7893218003610</v>
+        <v>50196081</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>365</v>
       </c>
       <c r="C352">
-        <v>5.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="D352" t="s">
         <v>54</v>
@@ -6455,27 +6446,27 @@
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" s="1">
-        <v>7893218003603</v>
+        <v>82184000328</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>366</v>
       </c>
       <c r="C353">
-        <v>6.99</v>
+        <v>149.99</v>
       </c>
       <c r="D353" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" s="1">
-        <v>7893218000473</v>
+        <v>5000281004020</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>367</v>
       </c>
       <c r="C354">
-        <v>39.99</v>
+        <v>149.99</v>
       </c>
       <c r="D354" t="s">
         <v>54</v>
@@ -6483,57 +6474,15 @@
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" s="1">
-        <v>50196081</v>
+        <v>5010106111956</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>368</v>
       </c>
       <c r="C355">
-        <v>69.989999999999995</v>
+        <v>99.99</v>
       </c>
       <c r="D355" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A356" s="1">
-        <v>82184000328</v>
-      </c>
-      <c r="B356" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="C356">
-        <v>149.99</v>
-      </c>
-      <c r="D356" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A357" s="1">
-        <v>5000281004020</v>
-      </c>
-      <c r="B357" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="C357">
-        <v>149.99</v>
-      </c>
-      <c r="D357" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A358" s="1">
-        <v>5010106111956</v>
-      </c>
-      <c r="B358" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C358">
-        <v>99.99</v>
-      </c>
-      <c r="D358" t="s">
         <v>54</v>
       </c>
     </row>

--- a/pitstop_produtos_categorizados_v2.xlsx
+++ b/pitstop_produtos_categorizados_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\super\Desktop\PitStop Manaira Delivery\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342A1211-DEE7-49F3-9345-7F5413B42E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{493979A5-958D-4603-9451-E4C2B8CB3487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="368">
   <si>
     <t>codigo_barras</t>
   </si>
@@ -144,9 +144,6 @@
     <t>AWE BEBIDA ENERGET.PITAYA/LICHIA 355ML</t>
   </si>
   <si>
-    <t>BANDEJA AMENDOIM SABORES KG</t>
-  </si>
-  <si>
     <t>BATATA SCRUSCH WAVE 50G</t>
   </si>
   <si>
@@ -822,9 +819,6 @@
     <t>PALITINHOS STIKSY ELMA CHIPS 160G</t>
   </si>
   <si>
-    <t>PALITOS BILLA ESPETINHOS DE BAMBU C/50</t>
-  </si>
-  <si>
     <t>PEPSI 1L</t>
   </si>
   <si>
@@ -1009,9 +1003,6 @@
   </si>
   <si>
     <t>SALGADINHO TORCIDA 60G QUEIJO</t>
-  </si>
-  <si>
-    <t>SALGADO MINEIRO DIVERSOS UN</t>
   </si>
   <si>
     <t>SCHWEPPES CITRUS KS 290ML</t>
@@ -1507,7 +1498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D355"/>
+  <dimension ref="A1:D352"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" style="1" bestFit="1" customWidth="1"/>
@@ -1807,7 +1798,7 @@
         <v>8.99</v>
       </c>
       <c r="D21" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1863,7 +1854,7 @@
         <v>16.989999999999998</v>
       </c>
       <c r="D25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1877,7 +1868,7 @@
         <v>16.989999999999998</v>
       </c>
       <c r="D26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1891,7 +1882,7 @@
         <v>16.989999999999998</v>
       </c>
       <c r="D27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1905,18 +1896,18 @@
         <v>16.989999999999998</v>
       </c>
       <c r="D28" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>763</v>
+        <v>7891091063103</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C29">
-        <v>49.99</v>
+        <v>4.49</v>
       </c>
       <c r="D29" t="s">
         <v>27</v>
@@ -1924,7 +1915,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>7891091063103</v>
+        <v>7891091063233</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>36</v>
@@ -1938,7 +1929,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>7891091063233</v>
+        <v>7891091063226</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>37</v>
@@ -1952,7 +1943,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>7891091063226</v>
+        <v>7891091063813</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>38</v>
@@ -1966,35 +1957,35 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>7891091063813</v>
+        <v>78912359</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C33">
-        <v>4.49</v>
+        <v>1.99</v>
       </c>
       <c r="D33" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>78912359</v>
+        <v>7891991307994</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C34">
-        <v>1.99</v>
+        <v>7.79</v>
       </c>
       <c r="D34" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>7891991307994</v>
+        <v>7891991307208</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>42</v>
@@ -2008,13 +1999,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>7891991307208</v>
+        <v>7891991307185</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C36">
-        <v>7.79</v>
+        <v>6.49</v>
       </c>
       <c r="D36" t="s">
         <v>20</v>
@@ -2022,21 +2013,21 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>7891991307185</v>
+        <v>7896213005962</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C37">
-        <v>6.49</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="D37" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>7896213005962</v>
+        <v>7896213005917</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>45</v>
@@ -2045,12 +2036,12 @@
         <v>2.4900000000000002</v>
       </c>
       <c r="D38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>7896213005917</v>
+        <v>7896213005924</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>46</v>
@@ -2059,12 +2050,12 @@
         <v>2.4900000000000002</v>
       </c>
       <c r="D39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>7896213005924</v>
+        <v>7896213005887</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>47</v>
@@ -2073,12 +2064,12 @@
         <v>2.4900000000000002</v>
       </c>
       <c r="D40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>7896213005887</v>
+        <v>7896213005894</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>48</v>
@@ -2087,12 +2078,12 @@
         <v>2.4900000000000002</v>
       </c>
       <c r="D41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>7896213005894</v>
+        <v>7896213005931</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>49</v>
@@ -2101,12 +2092,12 @@
         <v>2.4900000000000002</v>
       </c>
       <c r="D42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>7896213005931</v>
+        <v>7896213005948</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>50</v>
@@ -2115,12 +2106,12 @@
         <v>2.4900000000000002</v>
       </c>
       <c r="D43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>7896213005948</v>
+        <v>7896213005955</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>51</v>
@@ -2129,46 +2120,46 @@
         <v>2.4900000000000002</v>
       </c>
       <c r="D44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>7896213005955</v>
+        <v>7898206920016</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C45">
-        <v>2.4900000000000002</v>
+        <v>22.99</v>
       </c>
       <c r="D45" t="s">
-        <v>41</v>
+        <v>366</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>7898206920016</v>
+        <v>7898732900285</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C46">
-        <v>22.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="D46" t="s">
-        <v>369</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>7898732900285</v>
+        <v>7897326800130</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C47">
-        <v>79.989999999999995</v>
+        <v>29.99</v>
       </c>
       <c r="D47" t="s">
         <v>31</v>
@@ -2176,13 +2167,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>7897326800130</v>
+        <v>7897326800178</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C48">
-        <v>29.99</v>
+        <v>33.99</v>
       </c>
       <c r="D48" t="s">
         <v>31</v>
@@ -2190,13 +2181,13 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>7897326800178</v>
+        <v>7897326800246</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C49">
-        <v>33.99</v>
+        <v>39.99</v>
       </c>
       <c r="D49" t="s">
         <v>31</v>
@@ -2204,13 +2195,13 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>7897326800246</v>
+        <v>7897326800338</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C50">
-        <v>39.99</v>
+        <v>59.99</v>
       </c>
       <c r="D50" t="s">
         <v>31</v>
@@ -2218,13 +2209,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>7897326800338</v>
+        <v>7897326800451</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C51">
-        <v>59.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="D51" t="s">
         <v>31</v>
@@ -2232,13 +2223,13 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>7897326800451</v>
+        <v>7897326800086</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C52">
-        <v>79.989999999999995</v>
+        <v>17.989999999999998</v>
       </c>
       <c r="D52" t="s">
         <v>31</v>
@@ -2246,55 +2237,55 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>7897326800086</v>
+        <v>7896010006315</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C53">
-        <v>17.989999999999998</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="D53" t="s">
-        <v>31</v>
+        <v>366</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>7896010006315</v>
+        <v>7898377710027</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C54">
-        <v>69.989999999999995</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D54" t="s">
-        <v>369</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>7898377710027</v>
+        <v>40232790140</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C55">
-        <v>19.989999999999998</v>
+        <v>55.99</v>
       </c>
       <c r="D55" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>40232790140</v>
+        <v>40232790126</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C56">
-        <v>55.99</v>
+        <v>26.99</v>
       </c>
       <c r="D56" t="s">
         <v>31</v>
@@ -2302,27 +2293,27 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>40232790126</v>
+        <v>7896045505340</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C57">
-        <v>26.99</v>
+        <v>5.49</v>
       </c>
       <c r="D57" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>7896045505340</v>
+        <v>7896045506415</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C58">
-        <v>5.49</v>
+        <v>4.49</v>
       </c>
       <c r="D58" t="s">
         <v>20</v>
@@ -2330,13 +2321,13 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>7896045506415</v>
+        <v>7891991000796</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C59">
-        <v>4.49</v>
+        <v>3.79</v>
       </c>
       <c r="D59" t="s">
         <v>20</v>
@@ -2344,13 +2335,13 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>7891991000796</v>
+        <v>7891991010023</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C60">
-        <v>3.79</v>
+        <v>3.99</v>
       </c>
       <c r="D60" t="s">
         <v>20</v>
@@ -2358,13 +2349,13 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>7891991010023</v>
+        <v>7898230716616</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C61">
-        <v>3.99</v>
+        <v>6.99</v>
       </c>
       <c r="D61" t="s">
         <v>20</v>
@@ -2372,7 +2363,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>7898230716616</v>
+        <v>7898230716654</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>70</v>
@@ -2386,7 +2377,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>7898230716654</v>
+        <v>7898230716630</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>71</v>
@@ -2400,13 +2391,13 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>7898230716630</v>
+        <v>7891991006088</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C64">
-        <v>6.99</v>
+        <v>3.99</v>
       </c>
       <c r="D64" t="s">
         <v>20</v>
@@ -2414,13 +2405,13 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>7891991006088</v>
+        <v>7891991014236</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C65">
-        <v>3.99</v>
+        <v>5.19</v>
       </c>
       <c r="D65" t="s">
         <v>20</v>
@@ -2428,13 +2419,13 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>7891991014236</v>
+        <v>7891991294942</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C66">
-        <v>5.19</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="D66" t="s">
         <v>20</v>
@@ -2442,13 +2433,13 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>7891991294942</v>
+        <v>7891149010509</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C67">
-        <v>4.1900000000000004</v>
+        <v>4.49</v>
       </c>
       <c r="D67" t="s">
         <v>20</v>
@@ -2456,13 +2447,13 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>7891149010509</v>
+        <v>7891149104932</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C68">
-        <v>4.49</v>
+        <v>3.99</v>
       </c>
       <c r="D68" t="s">
         <v>20</v>
@@ -2470,13 +2461,13 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>7891149104932</v>
+        <v>7891149101528</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C69">
-        <v>3.99</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="D69" t="s">
         <v>20</v>
@@ -2484,13 +2475,13 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>7891149101528</v>
+        <v>7891991014762</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C70">
-        <v>4.8899999999999997</v>
+        <v>4.99</v>
       </c>
       <c r="D70" t="s">
         <v>20</v>
@@ -2498,13 +2489,13 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>7891991014762</v>
+        <v>7891991298421</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C71">
-        <v>4.99</v>
+        <v>5.89</v>
       </c>
       <c r="D71" t="s">
         <v>20</v>
@@ -2512,13 +2503,13 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>7891991298421</v>
+        <v>7891991010481</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C72">
-        <v>5.89</v>
+        <v>4.59</v>
       </c>
       <c r="D72" t="s">
         <v>20</v>
@@ -2526,13 +2517,13 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>7891991010481</v>
+        <v>7891991295055</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C73">
-        <v>4.59</v>
+        <v>5.99</v>
       </c>
       <c r="D73" t="s">
         <v>20</v>
@@ -2540,13 +2531,13 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>7891991295055</v>
+        <v>7891149108718</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C74">
-        <v>5.99</v>
+        <v>7.99</v>
       </c>
       <c r="D74" t="s">
         <v>20</v>
@@ -2554,13 +2545,13 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>7891149108718</v>
+        <v>7898367984056</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C75">
-        <v>7.99</v>
+        <v>5.99</v>
       </c>
       <c r="D75" t="s">
         <v>20</v>
@@ -2568,7 +2559,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>7898367984056</v>
+        <v>7898367984070</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>84</v>
@@ -2582,13 +2573,13 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>7898367984070</v>
+        <v>7898367980010</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C77">
-        <v>5.99</v>
+        <v>5.39</v>
       </c>
       <c r="D77" t="s">
         <v>20</v>
@@ -2596,13 +2587,13 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>7898367980010</v>
+        <v>7898367983790</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C78">
-        <v>5.39</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="D78" t="s">
         <v>20</v>
@@ -2610,13 +2601,13 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>7898367983790</v>
+        <v>7898367984346</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C79">
-        <v>4.1900000000000004</v>
+        <v>5.39</v>
       </c>
       <c r="D79" t="s">
         <v>20</v>
@@ -2624,13 +2615,13 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>7898367984346</v>
+        <v>7898367984377</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C80">
-        <v>5.39</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="D80" t="s">
         <v>20</v>
@@ -2638,13 +2629,13 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>7898367984377</v>
+        <v>78936683</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C81">
-        <v>4.1900000000000004</v>
+        <v>7.19</v>
       </c>
       <c r="D81" t="s">
         <v>20</v>
@@ -2652,7 +2643,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>78936683</v>
+        <v>7896045506040</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>90</v>
@@ -2666,13 +2657,13 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>7896045506040</v>
+        <v>7896045506910</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C83">
-        <v>7.19</v>
+        <v>6.99</v>
       </c>
       <c r="D83" t="s">
         <v>20</v>
@@ -2680,13 +2671,13 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>7896045506910</v>
+        <v>7896045506873</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C84">
-        <v>6.99</v>
+        <v>5.99</v>
       </c>
       <c r="D84" t="s">
         <v>20</v>
@@ -2694,13 +2685,13 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>7896045506873</v>
+        <v>78905498</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C85">
-        <v>5.99</v>
+        <v>13.99</v>
       </c>
       <c r="D85" t="s">
         <v>20</v>
@@ -2708,13 +2699,13 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>78905498</v>
+        <v>7891991299619</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C86">
-        <v>13.99</v>
+        <v>6.99</v>
       </c>
       <c r="D86" t="s">
         <v>20</v>
@@ -2722,13 +2713,13 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>7891991299619</v>
+        <v>7891991302029</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C87">
-        <v>6.99</v>
+        <v>6.79</v>
       </c>
       <c r="D87" t="s">
         <v>20</v>
@@ -2736,13 +2727,13 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>7891991302029</v>
+        <v>7891991015493</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C88">
-        <v>6.79</v>
+        <v>4.99</v>
       </c>
       <c r="D88" t="s">
         <v>20</v>
@@ -2750,13 +2741,13 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>7891991015493</v>
+        <v>7891991297479</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C89">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
       <c r="D89" t="s">
         <v>20</v>
@@ -2764,13 +2755,13 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>7891991297479</v>
+        <v>7891991297424</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C90">
-        <v>5.99</v>
+        <v>4.99</v>
       </c>
       <c r="D90" t="s">
         <v>20</v>
@@ -2778,13 +2769,13 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>7891991297424</v>
+        <v>7891991015462</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C91">
-        <v>4.99</v>
+        <v>6.69</v>
       </c>
       <c r="D91" t="s">
         <v>20</v>
@@ -2792,13 +2783,13 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>7891991015462</v>
+        <v>7891991016223</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C92">
-        <v>6.69</v>
+        <v>5.39</v>
       </c>
       <c r="D92" t="s">
         <v>20</v>
@@ -2806,13 +2797,13 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>7891991016223</v>
+        <v>7891991295109</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C93">
-        <v>5.39</v>
+        <v>12.99</v>
       </c>
       <c r="D93" t="s">
         <v>20</v>
@@ -2820,13 +2811,13 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>7891991295109</v>
+        <v>7891991304870</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C94">
-        <v>12.99</v>
+        <v>7.99</v>
       </c>
       <c r="D94" t="s">
         <v>20</v>
@@ -2834,27 +2825,27 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>7891991304870</v>
+        <v>7891098040985</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C95">
-        <v>7.99</v>
+        <v>7.49</v>
       </c>
       <c r="D95" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>7891098040985</v>
+        <v>7891098040886</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C96">
-        <v>7.49</v>
+        <v>3.99</v>
       </c>
       <c r="D96" t="s">
         <v>31</v>
@@ -2862,231 +2853,231 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>7891098040886</v>
+        <v>7891141015267</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C97">
-        <v>3.99</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D97" t="s">
-        <v>31</v>
+        <v>177</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>7891141015267</v>
+        <v>7891000436837</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C98">
-        <v>19.989999999999998</v>
+        <v>3.49</v>
       </c>
       <c r="D98" t="s">
-        <v>178</v>
+        <v>40</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>7891000436837</v>
+        <v>8712000025649</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C99">
-        <v>3.49</v>
+        <v>119.99</v>
       </c>
       <c r="D99" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>8712000025649</v>
+        <v>3000</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C100">
-        <v>119.99</v>
+        <v>3.29</v>
       </c>
       <c r="D100" t="s">
-        <v>20</v>
+        <v>109</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>3000</v>
+        <v>7894900011753</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C101">
-        <v>3.29</v>
+        <v>7.99</v>
       </c>
       <c r="D101" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>7894900011753</v>
+        <v>7894900701753</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C102">
-        <v>7.99</v>
+        <v>7.49</v>
       </c>
       <c r="D102" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>7894900701753</v>
+        <v>7894900027099</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C103">
-        <v>7.49</v>
+        <v>4.79</v>
       </c>
       <c r="D103" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>7894900027099</v>
+        <v>7894900701715</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C104">
-        <v>4.79</v>
+        <v>6.49</v>
       </c>
       <c r="D104" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>7894900701715</v>
+        <v>7894900027044</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>114</v>
       </c>
       <c r="C105">
-        <v>6.49</v>
+        <v>6.99</v>
       </c>
       <c r="D105" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>7894900027044</v>
+        <v>7894900027020</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C106">
-        <v>6.99</v>
+        <v>11.79</v>
       </c>
       <c r="D106" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>7894900027020</v>
+        <v>7894900010398</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C107">
-        <v>11.79</v>
+        <v>2.79</v>
       </c>
       <c r="D107" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>7894900010398</v>
+        <v>7894900025019</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C108">
-        <v>2.79</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="D108" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>7894900025019</v>
+        <v>7894900700398</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C109">
-        <v>2.4900000000000002</v>
+        <v>2.69</v>
       </c>
       <c r="D109" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>7894900700398</v>
+        <v>78912939</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C110">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="D110" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>78912939</v>
+        <v>78909045</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C111">
-        <v>2.59</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="D111" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>78909045</v>
+        <v>7894900027082</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C112">
-        <v>2.4900000000000002</v>
+        <v>7.99</v>
       </c>
       <c r="D112" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>7894900027082</v>
+        <v>7894900014211</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>122</v>
@@ -3095,26 +3086,26 @@
         <v>7.99</v>
       </c>
       <c r="D113" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>7894900014211</v>
+        <v>3004</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C114">
-        <v>7.99</v>
+        <v>10.49</v>
       </c>
       <c r="D114" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>3004</v>
+        <v>7894900701517</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>124</v>
@@ -3123,166 +3114,166 @@
         <v>10.49</v>
       </c>
       <c r="D115" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>7894900701517</v>
+        <v>7894900027013</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>125</v>
       </c>
       <c r="C116">
-        <v>10.49</v>
+        <v>10.79</v>
       </c>
       <c r="D116" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>7894900027013</v>
+        <v>7894900010015</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C117">
-        <v>10.79</v>
+        <v>3.79</v>
       </c>
       <c r="D117" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>7894900010015</v>
+        <v>7894900700015</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C118">
-        <v>3.79</v>
+        <v>3.69</v>
       </c>
       <c r="D118" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>7894900700015</v>
+        <v>7894900013566</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C119">
-        <v>3.69</v>
+        <v>4.29</v>
       </c>
       <c r="D119" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>7894900013566</v>
+        <v>7894900703566</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C120">
-        <v>4.29</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="D120" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>7894900703566</v>
+        <v>7894900705034</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C121">
-        <v>4.1900000000000004</v>
+        <v>3.49</v>
       </c>
       <c r="D121" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>7894900705034</v>
+        <v>7898341430111</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C122">
-        <v>3.49</v>
+        <v>9.2899999999999991</v>
       </c>
       <c r="D122" t="s">
-        <v>110</v>
+        <v>367</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>7898341430111</v>
+        <v>7898341430098</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C123">
-        <v>9.2899999999999991</v>
+        <v>8.99</v>
       </c>
       <c r="D123" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>7898341430098</v>
+        <v>7898341430777</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C124">
-        <v>8.99</v>
+        <v>9.2899999999999991</v>
       </c>
       <c r="D124" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>7898341430777</v>
+        <v>7894900550061</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>134</v>
       </c>
       <c r="C125">
-        <v>9.2899999999999991</v>
+        <v>6.99</v>
       </c>
       <c r="D125" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>7894900550061</v>
+        <v>7894900556056</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C126">
-        <v>6.99</v>
+        <v>3.79</v>
       </c>
       <c r="D126" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
-        <v>7894900556056</v>
+        <v>7894900559019</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>136</v>
@@ -3291,26 +3282,26 @@
         <v>3.79</v>
       </c>
       <c r="D127" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
-        <v>7894900559019</v>
+        <v>7894900666526</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C128">
-        <v>3.79</v>
+        <v>6.99</v>
       </c>
       <c r="D128" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
-        <v>7894900666526</v>
+        <v>7894900556063</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>138</v>
@@ -3319,26 +3310,26 @@
         <v>6.99</v>
       </c>
       <c r="D129" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
-        <v>7894900556063</v>
+        <v>7894900666502</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C130">
-        <v>6.99</v>
+        <v>3.79</v>
       </c>
       <c r="D130" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
-        <v>7894900666502</v>
+        <v>7894900550054</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>140</v>
@@ -3347,26 +3338,26 @@
         <v>3.79</v>
       </c>
       <c r="D131" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
-        <v>7894900550054</v>
+        <v>7898080664563</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C132">
-        <v>3.79</v>
+        <v>15.99</v>
       </c>
       <c r="D132" t="s">
-        <v>370</v>
+        <v>156</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
-        <v>7898080664563</v>
+        <v>7898080664389</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>142</v>
@@ -3375,12 +3366,12 @@
         <v>15.99</v>
       </c>
       <c r="D133" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
-        <v>7898080664389</v>
+        <v>7898080662668</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>143</v>
@@ -3389,12 +3380,12 @@
         <v>15.99</v>
       </c>
       <c r="D134" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
-        <v>7898080662668</v>
+        <v>7898080665409</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>144</v>
@@ -3403,26 +3394,26 @@
         <v>15.99</v>
       </c>
       <c r="D135" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
-        <v>7898080665409</v>
+        <v>7898080664396</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C136">
-        <v>15.99</v>
+        <v>7.99</v>
       </c>
       <c r="D136" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
-        <v>7898080664396</v>
+        <v>7898080664587</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>146</v>
@@ -3431,12 +3422,12 @@
         <v>7.99</v>
       </c>
       <c r="D137" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
-        <v>7898080664587</v>
+        <v>7898080665416</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>147</v>
@@ -3445,12 +3436,12 @@
         <v>7.99</v>
       </c>
       <c r="D138" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
-        <v>7898080665416</v>
+        <v>7898080665003</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>148</v>
@@ -3459,12 +3450,12 @@
         <v>7.99</v>
       </c>
       <c r="D139" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
-        <v>7898080665003</v>
+        <v>7898080664815</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>149</v>
@@ -3473,12 +3464,12 @@
         <v>7.99</v>
       </c>
       <c r="D140" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
-        <v>7898080664815</v>
+        <v>7898080664839</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>150</v>
@@ -3487,12 +3478,12 @@
         <v>7.99</v>
       </c>
       <c r="D141" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
-        <v>7898080664839</v>
+        <v>7898080664662</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>151</v>
@@ -3501,12 +3492,12 @@
         <v>7.99</v>
       </c>
       <c r="D142" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
-        <v>7898080664662</v>
+        <v>7898080665447</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>152</v>
@@ -3515,12 +3506,12 @@
         <v>7.99</v>
       </c>
       <c r="D143" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
-        <v>7898080665447</v>
+        <v>7898080664808</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>153</v>
@@ -3529,12 +3520,12 @@
         <v>7.99</v>
       </c>
       <c r="D144" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
-        <v>7898080664808</v>
+        <v>7898080663733</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>154</v>
@@ -3543,40 +3534,40 @@
         <v>7.99</v>
       </c>
       <c r="D145" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
-        <v>7898080663733</v>
+        <v>70847022305</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>155</v>
       </c>
       <c r="C146">
-        <v>7.99</v>
+        <v>10.99</v>
       </c>
       <c r="D146" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
-        <v>70847022305</v>
+        <v>70847022015</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C147">
         <v>10.99</v>
       </c>
       <c r="D147" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
-        <v>70847022015</v>
+        <v>7898938890076</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>158</v>
@@ -3585,12 +3576,12 @@
         <v>10.99</v>
       </c>
       <c r="D148" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
-        <v>7898938890076</v>
+        <v>7898938890120</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>159</v>
@@ -3599,12 +3590,12 @@
         <v>10.99</v>
       </c>
       <c r="D149" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
-        <v>7898938890120</v>
+        <v>1220000250147</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>160</v>
@@ -3613,12 +3604,12 @@
         <v>10.99</v>
       </c>
       <c r="D150" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
-        <v>1220000250147</v>
+        <v>70847034803</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>161</v>
@@ -3627,12 +3618,12 @@
         <v>10.99</v>
       </c>
       <c r="D151" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
-        <v>70847034803</v>
+        <v>70847033301</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>162</v>
@@ -3641,12 +3632,12 @@
         <v>10.99</v>
       </c>
       <c r="D152" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
-        <v>70847033301</v>
+        <v>7898938890113</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>163</v>
@@ -3655,12 +3646,12 @@
         <v>10.99</v>
       </c>
       <c r="D153" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
-        <v>7898938890113</v>
+        <v>1220000250031</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>164</v>
@@ -3669,12 +3660,12 @@
         <v>10.99</v>
       </c>
       <c r="D154" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
-        <v>1220000250031</v>
+        <v>1220000250222</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>165</v>
@@ -3683,12 +3674,12 @@
         <v>10.99</v>
       </c>
       <c r="D155" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
-        <v>1220000250222</v>
+        <v>70847022206</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>166</v>
@@ -3697,12 +3688,12 @@
         <v>10.99</v>
       </c>
       <c r="D156" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
-        <v>70847022206</v>
+        <v>7898938890090</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>167</v>
@@ -3711,12 +3702,12 @@
         <v>10.99</v>
       </c>
       <c r="D157" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
-        <v>7898938890090</v>
+        <v>70847033929</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>168</v>
@@ -3725,12 +3716,12 @@
         <v>10.99</v>
       </c>
       <c r="D158" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
-        <v>70847033929</v>
+        <v>7898947845685</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>169</v>
@@ -3739,124 +3730,124 @@
         <v>10.99</v>
       </c>
       <c r="D159" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
-        <v>7898947845685</v>
+        <v>7898947845753</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>170</v>
       </c>
       <c r="C160">
-        <v>10.99</v>
+        <v>14.99</v>
       </c>
       <c r="D160" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
-        <v>7898947845753</v>
+        <v>7899465200406</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>171</v>
       </c>
       <c r="C161">
-        <v>14.99</v>
+        <v>6.49</v>
       </c>
       <c r="D161" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
-        <v>7899465200406</v>
+        <v>7899465201854</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>172</v>
       </c>
       <c r="C162">
-        <v>6.49</v>
+        <v>18.989999999999998</v>
       </c>
       <c r="D162" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
-        <v>7899465201854</v>
+        <v>7899465200390</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C163">
-        <v>18.989999999999998</v>
+        <v>7.99</v>
       </c>
       <c r="D163" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
-        <v>7899465200390</v>
+        <v>7899465200987</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C164">
-        <v>7.99</v>
+        <v>8.49</v>
       </c>
       <c r="D164" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
-        <v>7899465200987</v>
+        <v>7899465200444</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>175</v>
       </c>
       <c r="C165">
-        <v>8.49</v>
+        <v>6.99</v>
       </c>
       <c r="D165" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
-        <v>7899465200444</v>
+        <v>7896452112582</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C166">
-        <v>6.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="D166" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
-        <v>7896452112582</v>
+        <v>7896034300802</v>
       </c>
       <c r="B167" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C167">
+        <v>18.989999999999998</v>
+      </c>
+      <c r="D167" t="s">
         <v>177</v>
-      </c>
-      <c r="C167">
-        <v>64.989999999999995</v>
-      </c>
-      <c r="D167" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
-        <v>7896034300802</v>
+        <v>7896034300239</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>179</v>
@@ -3865,26 +3856,26 @@
         <v>18.989999999999998</v>
       </c>
       <c r="D168" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
-        <v>7896034300239</v>
+        <v>7896023082979</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>180</v>
       </c>
       <c r="C169">
-        <v>18.989999999999998</v>
+        <v>49.99</v>
       </c>
       <c r="D169" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
-        <v>7896023082979</v>
+        <v>7896023082634</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>181</v>
@@ -3893,172 +3884,172 @@
         <v>49.99</v>
       </c>
       <c r="D170" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
-        <v>7896023082634</v>
+        <v>7894900030396</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>182</v>
       </c>
       <c r="C171">
-        <v>49.99</v>
+        <v>2.19</v>
       </c>
       <c r="D171" t="s">
-        <v>178</v>
+        <v>109</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
-        <v>7894900030396</v>
+        <v>3001</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>183</v>
       </c>
       <c r="C172">
-        <v>2.19</v>
+        <v>3.29</v>
       </c>
       <c r="D172" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
-        <v>3001</v>
+        <v>7894900031515</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C173">
-        <v>3.29</v>
+        <v>8.99</v>
       </c>
       <c r="D173" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
-        <v>7894900031515</v>
+        <v>7894900034219</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>185</v>
       </c>
       <c r="C174">
-        <v>8.99</v>
+        <v>7.99</v>
       </c>
       <c r="D174" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
-        <v>7894900034219</v>
+        <v>7894900030013</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C175">
-        <v>7.99</v>
+        <v>2.99</v>
       </c>
       <c r="D175" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
-        <v>7894900030013</v>
+        <v>7894900150018</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>187</v>
       </c>
       <c r="C176">
-        <v>2.99</v>
+        <v>2.79</v>
       </c>
       <c r="D176" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
-        <v>7894900150018</v>
+        <v>78912922</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>188</v>
       </c>
       <c r="C177">
-        <v>2.79</v>
+        <v>1.99</v>
       </c>
       <c r="D177" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
-        <v>78912922</v>
+        <v>7894900051513</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>189</v>
       </c>
       <c r="C178">
-        <v>1.99</v>
+        <v>8.99</v>
       </c>
       <c r="D178" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
-        <v>7894900051513</v>
+        <v>7894900050011</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C179">
-        <v>8.99</v>
+        <v>2.99</v>
       </c>
       <c r="D179" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
-        <v>7894900050011</v>
+        <v>78909052</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>191</v>
       </c>
       <c r="C180">
-        <v>2.99</v>
+        <v>1.99</v>
       </c>
       <c r="D180" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
-        <v>78909052</v>
+        <v>961</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>192</v>
       </c>
       <c r="C181">
-        <v>1.99</v>
+        <v>31.99</v>
       </c>
       <c r="D181" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
-        <v>961</v>
+        <v>7898399910627</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>193</v>
       </c>
       <c r="C182">
-        <v>31.99</v>
+        <v>4.49</v>
       </c>
       <c r="D182" t="s">
         <v>31</v>
@@ -4066,7 +4057,7 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
-        <v>7898399910627</v>
+        <v>7898043425019</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>194</v>
@@ -4080,41 +4071,41 @@
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
-        <v>7898043425019</v>
+        <v>5000291020706</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>195</v>
       </c>
       <c r="C184">
-        <v>4.49</v>
+        <v>129.99</v>
       </c>
       <c r="D184" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
-        <v>5000291020706</v>
+        <v>7622300847791</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>196</v>
       </c>
       <c r="C185">
-        <v>129.99</v>
+        <v>7.49</v>
       </c>
       <c r="D185" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
-        <v>7622300847791</v>
+        <v>7895800304235</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>197</v>
       </c>
       <c r="C186">
-        <v>7.49</v>
+        <v>2.99</v>
       </c>
       <c r="D186" t="s">
         <v>31</v>
@@ -4122,7 +4113,7 @@
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
-        <v>7895800304235</v>
+        <v>7622210564313</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>198</v>
@@ -4136,7 +4127,7 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
-        <v>7622210564313</v>
+        <v>7895800304211</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>199</v>
@@ -4150,7 +4141,7 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
-        <v>7895800304211</v>
+        <v>7622210564290</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>200</v>
@@ -4164,7 +4155,7 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
-        <v>7622210564290</v>
+        <v>7895800309780</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>201</v>
@@ -4178,7 +4169,7 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
-        <v>7895800309780</v>
+        <v>7895800304228</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>202</v>
@@ -4192,7 +4183,7 @@
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
-        <v>7895800304228</v>
+        <v>7895800201503</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>203</v>
@@ -4206,7 +4197,7 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
-        <v>7895800201503</v>
+        <v>7895800430002</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>204</v>
@@ -4220,35 +4211,35 @@
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
-        <v>7895800430002</v>
+        <v>7891991016124</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>205</v>
       </c>
       <c r="C194">
-        <v>2.99</v>
+        <v>1.99</v>
       </c>
       <c r="D194" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
-        <v>7891991016124</v>
+        <v>7891991002561</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>206</v>
       </c>
       <c r="C195">
-        <v>1.99</v>
+        <v>5.49</v>
       </c>
       <c r="D195" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
-        <v>7891991002561</v>
+        <v>7891991002608</v>
       </c>
       <c r="B196" s="2" t="s">
         <v>207</v>
@@ -4257,40 +4248,40 @@
         <v>5.49</v>
       </c>
       <c r="D196" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
-        <v>7891991002608</v>
+        <v>7891991014908</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>208</v>
       </c>
       <c r="C197">
-        <v>5.49</v>
+        <v>1.99</v>
       </c>
       <c r="D197" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
-        <v>7891991014908</v>
+        <v>7891991001342</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>209</v>
       </c>
       <c r="C198">
-        <v>1.99</v>
+        <v>8.59</v>
       </c>
       <c r="D198" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
-        <v>7891991001342</v>
+        <v>7891991001373</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>210</v>
@@ -4299,26 +4290,26 @@
         <v>8.59</v>
       </c>
       <c r="D199" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
-        <v>7891991001373</v>
+        <v>7891991000826</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>211</v>
       </c>
       <c r="C200">
-        <v>8.59</v>
+        <v>2.99</v>
       </c>
       <c r="D200" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
-        <v>7891991000826</v>
+        <v>7891991000727</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>212</v>
@@ -4327,138 +4318,138 @@
         <v>2.99</v>
       </c>
       <c r="D201" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
-        <v>7891991000727</v>
+        <v>7894900911510</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>213</v>
       </c>
       <c r="C202">
-        <v>2.99</v>
+        <v>7.49</v>
       </c>
       <c r="D202" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
-        <v>7894900911510</v>
+        <v>7894900910018</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>214</v>
       </c>
       <c r="C203">
-        <v>7.49</v>
+        <v>2.79</v>
       </c>
       <c r="D203" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
-        <v>7894900910018</v>
+        <v>7894900920017</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>215</v>
       </c>
       <c r="C204">
-        <v>2.79</v>
+        <v>2.59</v>
       </c>
       <c r="D204" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
-        <v>7894900920017</v>
+        <v>7894900921519</v>
       </c>
       <c r="B205" s="2" t="s">
         <v>216</v>
       </c>
       <c r="C205">
-        <v>2.59</v>
+        <v>7.49</v>
       </c>
       <c r="D205" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
-        <v>7894900921519</v>
+        <v>7892840812850</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>217</v>
       </c>
       <c r="C206">
-        <v>7.49</v>
+        <v>4.79</v>
       </c>
       <c r="D206" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
-        <v>7892840812850</v>
+        <v>7892840812416</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>218</v>
       </c>
       <c r="C207">
-        <v>4.79</v>
+        <v>8.69</v>
       </c>
       <c r="D207" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
-        <v>7892840812416</v>
+        <v>7892840812423</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>219</v>
       </c>
       <c r="C208">
-        <v>8.69</v>
+        <v>4.79</v>
       </c>
       <c r="D208" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
-        <v>7892840812423</v>
+        <v>7892840812874</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>220</v>
       </c>
       <c r="C209">
-        <v>4.79</v>
+        <v>8.49</v>
       </c>
       <c r="D209" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
-        <v>7892840812874</v>
+        <v>78938793</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>221</v>
       </c>
       <c r="C210">
-        <v>8.49</v>
+        <v>1.99</v>
       </c>
       <c r="D210" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
-        <v>78938793</v>
+        <v>78938816</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>222</v>
@@ -4472,7 +4463,7 @@
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
-        <v>78938816</v>
+        <v>78938854</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>223</v>
@@ -4486,7 +4477,7 @@
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
-        <v>78938854</v>
+        <v>78938830</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>224</v>
@@ -4500,7 +4491,7 @@
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
-        <v>78938830</v>
+        <v>78938878</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>225</v>
@@ -4514,7 +4505,7 @@
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
-        <v>78938878</v>
+        <v>78938823</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>226</v>
@@ -4528,7 +4519,7 @@
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
-        <v>78938823</v>
+        <v>78938847</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>227</v>
@@ -4542,7 +4533,7 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
-        <v>78938847</v>
+        <v>78938861</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>228</v>
@@ -4556,77 +4547,77 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
-        <v>78938861</v>
+        <v>7898906925021</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>229</v>
       </c>
       <c r="C218">
-        <v>1.99</v>
+        <v>29.99</v>
       </c>
       <c r="D218" t="s">
-        <v>31</v>
+        <v>366</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
-        <v>7898906925021</v>
+        <v>7898906925281</v>
       </c>
       <c r="B219" s="2" t="s">
         <v>230</v>
       </c>
       <c r="C219">
-        <v>29.99</v>
+        <v>47.99</v>
       </c>
       <c r="D219" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
-        <v>7898906925281</v>
+        <v>7898906925038</v>
       </c>
       <c r="B220" s="2" t="s">
         <v>231</v>
       </c>
       <c r="C220">
-        <v>47.99</v>
+        <v>39.99</v>
       </c>
       <c r="D220" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
-        <v>7898906925038</v>
+        <v>7898906925076</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>232</v>
       </c>
       <c r="C221">
-        <v>39.99</v>
+        <v>7.99</v>
       </c>
       <c r="D221" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
-        <v>7898906925076</v>
+        <v>7898906925236</v>
       </c>
       <c r="B222" s="2" t="s">
         <v>233</v>
       </c>
       <c r="C222">
-        <v>7.99</v>
+        <v>16.989999999999998</v>
       </c>
       <c r="D222" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
-        <v>7898906925236</v>
+        <v>7898906925557</v>
       </c>
       <c r="B223" s="2" t="s">
         <v>234</v>
@@ -4635,12 +4626,12 @@
         <v>16.989999999999998</v>
       </c>
       <c r="D223" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
-        <v>7898906925557</v>
+        <v>7898906925472</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>235</v>
@@ -4649,40 +4640,40 @@
         <v>16.989999999999998</v>
       </c>
       <c r="D224" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
-        <v>7898906925472</v>
+        <v>7898906925212</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>236</v>
       </c>
       <c r="C225">
-        <v>16.989999999999998</v>
+        <v>11.99</v>
       </c>
       <c r="D225" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
-        <v>7898906925212</v>
+        <v>7898906925519</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>237</v>
       </c>
       <c r="C226">
-        <v>11.99</v>
+        <v>16.989999999999998</v>
       </c>
       <c r="D226" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
-        <v>7898906925519</v>
+        <v>7898906925274</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>238</v>
@@ -4691,12 +4682,12 @@
         <v>16.989999999999998</v>
       </c>
       <c r="D227" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
-        <v>7898906925274</v>
+        <v>7898906925229</v>
       </c>
       <c r="B228" s="2" t="s">
         <v>239</v>
@@ -4705,26 +4696,26 @@
         <v>16.989999999999998</v>
       </c>
       <c r="D228" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
-        <v>7898906925229</v>
+        <v>7898906925618</v>
       </c>
       <c r="B229" s="2" t="s">
         <v>240</v>
       </c>
       <c r="C229">
-        <v>16.989999999999998</v>
+        <v>12.99</v>
       </c>
       <c r="D229" t="s">
-        <v>369</v>
+        <v>53</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
-        <v>7898906925618</v>
+        <v>7898906925656</v>
       </c>
       <c r="B230" s="2" t="s">
         <v>241</v>
@@ -4733,12 +4724,12 @@
         <v>12.99</v>
       </c>
       <c r="D230" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
-        <v>7898906925656</v>
+        <v>7898906925632</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>242</v>
@@ -4747,12 +4738,12 @@
         <v>12.99</v>
       </c>
       <c r="D231" t="s">
-        <v>54</v>
+        <v>366</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
-        <v>7898906925632</v>
+        <v>7898906925601</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>243</v>
@@ -4761,26 +4752,26 @@
         <v>12.99</v>
       </c>
       <c r="D232" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
-        <v>7898906925601</v>
+        <v>80878018</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>244</v>
       </c>
       <c r="C233">
-        <v>12.99</v>
+        <v>3.49</v>
       </c>
       <c r="D233" t="s">
-        <v>369</v>
+        <v>31</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
-        <v>80878018</v>
+        <v>80935513</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>245</v>
@@ -4794,13 +4785,13 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
-        <v>80935513</v>
+        <v>7895144603063</v>
       </c>
       <c r="B235" s="2" t="s">
         <v>246</v>
       </c>
       <c r="C235">
-        <v>3.49</v>
+        <v>2.99</v>
       </c>
       <c r="D235" t="s">
         <v>31</v>
@@ -4808,7 +4799,7 @@
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
-        <v>7895144603063</v>
+        <v>7896262304306</v>
       </c>
       <c r="B236" s="2" t="s">
         <v>247</v>
@@ -4822,7 +4813,7 @@
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
-        <v>7896262304306</v>
+        <v>7895144603148</v>
       </c>
       <c r="B237" s="2" t="s">
         <v>248</v>
@@ -4836,7 +4827,7 @@
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
-        <v>7895144603148</v>
+        <v>7895144603223</v>
       </c>
       <c r="B238" s="2" t="s">
         <v>249</v>
@@ -4850,7 +4841,7 @@
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
-        <v>7895144603223</v>
+        <v>7895144603087</v>
       </c>
       <c r="B239" s="2" t="s">
         <v>250</v>
@@ -4864,13 +4855,13 @@
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
-        <v>7895144603087</v>
+        <v>7895144297590</v>
       </c>
       <c r="B240" s="2" t="s">
         <v>251</v>
       </c>
       <c r="C240">
-        <v>2.99</v>
+        <v>12.99</v>
       </c>
       <c r="D240" t="s">
         <v>31</v>
@@ -4878,7 +4869,7 @@
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
-        <v>7895144297590</v>
+        <v>78922327</v>
       </c>
       <c r="B241" s="2" t="s">
         <v>252</v>
@@ -4892,7 +4883,7 @@
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
-        <v>78922327</v>
+        <v>7895144295664</v>
       </c>
       <c r="B242" s="2" t="s">
         <v>253</v>
@@ -4906,7 +4897,7 @@
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
-        <v>7895144295664</v>
+        <v>78922310</v>
       </c>
       <c r="B243" s="2" t="s">
         <v>254</v>
@@ -4920,7 +4911,7 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
-        <v>78922310</v>
+        <v>7895144899978</v>
       </c>
       <c r="B244" s="2" t="s">
         <v>255</v>
@@ -4934,7 +4925,7 @@
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
-        <v>7895144899978</v>
+        <v>78922334</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>256</v>
@@ -4948,7 +4939,7 @@
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
-        <v>78922334</v>
+        <v>7895144293080</v>
       </c>
       <c r="B246" s="2" t="s">
         <v>257</v>
@@ -4962,13 +4953,13 @@
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
-        <v>7895144293080</v>
+        <v>7895144899930</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>258</v>
       </c>
       <c r="C247">
-        <v>12.99</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="D247" t="s">
         <v>31</v>
@@ -4976,147 +4967,147 @@
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
-        <v>7895144899930</v>
+        <v>7892840822613</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>259</v>
       </c>
       <c r="C248">
-        <v>2.4900000000000002</v>
+        <v>10.99</v>
       </c>
       <c r="D248" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
-        <v>7892840822613</v>
+        <v>7892840800406</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>260</v>
       </c>
       <c r="C249">
-        <v>10.99</v>
+        <v>5.19</v>
       </c>
       <c r="D249" t="s">
-        <v>27</v>
+        <v>109</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
-        <v>7898918339229</v>
+        <v>7892840800000</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>261</v>
       </c>
       <c r="C250">
-        <v>2.99</v>
+        <v>7.99</v>
       </c>
       <c r="D250" t="s">
-        <v>27</v>
+        <v>109</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
-        <v>7892840800406</v>
+        <v>7892840800079</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>262</v>
       </c>
       <c r="C251">
-        <v>5.19</v>
+        <v>2.99</v>
       </c>
       <c r="D251" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
-        <v>7892840800000</v>
+        <v>7892840820862</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>263</v>
       </c>
       <c r="C252">
-        <v>7.99</v>
+        <v>5.19</v>
       </c>
       <c r="D252" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
-        <v>7892840800079</v>
+        <v>7892840800567</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>264</v>
       </c>
       <c r="C253">
-        <v>2.99</v>
+        <v>1.99</v>
       </c>
       <c r="D253" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
-        <v>7892840820862</v>
+        <v>7892840813444</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>265</v>
       </c>
       <c r="C254">
-        <v>5.19</v>
+        <v>8.39</v>
       </c>
       <c r="D254" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
-        <v>7892840800567</v>
+        <v>7892840813505</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>266</v>
       </c>
       <c r="C255">
-        <v>1.99</v>
+        <v>2.99</v>
       </c>
       <c r="D255" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
-        <v>7892840813444</v>
+        <v>7898339040421</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>267</v>
       </c>
       <c r="C256">
-        <v>8.39</v>
+        <v>6.99</v>
       </c>
       <c r="D256" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
-        <v>7892840813505</v>
+        <v>7898339041459</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>268</v>
       </c>
       <c r="C257">
-        <v>2.99</v>
+        <v>6.99</v>
       </c>
       <c r="D257" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
-        <v>7898339040421</v>
+        <v>7898339040407</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>269</v>
@@ -5130,77 +5121,77 @@
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
-        <v>7898339041459</v>
+        <v>7891075020023</v>
       </c>
       <c r="B259" s="2" t="s">
         <v>270</v>
       </c>
       <c r="C259">
-        <v>6.99</v>
+        <v>8.99</v>
       </c>
       <c r="D259" t="s">
-        <v>31</v>
+        <v>271</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
-        <v>7898339040407</v>
+        <v>7891150094321</v>
       </c>
       <c r="B260" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C260">
+        <v>8.99</v>
+      </c>
+      <c r="D260" t="s">
         <v>271</v>
-      </c>
-      <c r="C260">
-        <v>6.99</v>
-      </c>
-      <c r="D260" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
-        <v>7891075020023</v>
+        <v>7891075010130</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C261">
         <v>8.99</v>
       </c>
       <c r="D261" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
-        <v>7891150094321</v>
+        <v>7891150064904</v>
       </c>
       <c r="B262" s="2" t="s">
         <v>274</v>
       </c>
       <c r="C262">
-        <v>8.99</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D262" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
-        <v>7891075010130</v>
+        <v>7891150023093</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>275</v>
       </c>
       <c r="C263">
-        <v>8.99</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D263" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
-        <v>7891150064904</v>
+        <v>7891075403215</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>276</v>
@@ -5209,12 +5200,12 @@
         <v>19.989999999999998</v>
       </c>
       <c r="D264" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
-        <v>7891150023093</v>
+        <v>7891150041042</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>277</v>
@@ -5223,12 +5214,12 @@
         <v>19.989999999999998</v>
       </c>
       <c r="D265" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
-        <v>7891075403215</v>
+        <v>7891150081963</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>278</v>
@@ -5237,40 +5228,40 @@
         <v>19.989999999999998</v>
       </c>
       <c r="D266" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
-        <v>7891150041042</v>
+        <v>7891150099937</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>279</v>
       </c>
       <c r="C267">
-        <v>19.989999999999998</v>
+        <v>10.99</v>
       </c>
       <c r="D267" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
-        <v>7891150081963</v>
+        <v>7891075060210</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>280</v>
       </c>
       <c r="C268">
-        <v>19.989999999999998</v>
+        <v>10.99</v>
       </c>
       <c r="D268" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
-        <v>7891150099937</v>
+        <v>7891150089051</v>
       </c>
       <c r="B269" s="2" t="s">
         <v>281</v>
@@ -5279,96 +5270,96 @@
         <v>10.99</v>
       </c>
       <c r="D269" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
-        <v>7891075060210</v>
+        <v>7897326802011</v>
       </c>
       <c r="B270" s="2" t="s">
         <v>282</v>
       </c>
       <c r="C270">
-        <v>10.99</v>
+        <v>13.99</v>
       </c>
       <c r="D270" t="s">
-        <v>273</v>
+        <v>31</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
-        <v>7891150089051</v>
+        <v>7894900503029</v>
       </c>
       <c r="B271" s="2" t="s">
         <v>283</v>
       </c>
       <c r="C271">
-        <v>10.99</v>
+        <v>5.49</v>
       </c>
       <c r="D271" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
-        <v>7897326802011</v>
+        <v>7894900501001</v>
       </c>
       <c r="B272" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C272">
+        <v>5.49</v>
+      </c>
+      <c r="D272" t="s">
         <v>284</v>
-      </c>
-      <c r="C272">
-        <v>13.99</v>
-      </c>
-      <c r="D272" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
-        <v>7894900503029</v>
+        <v>7898275016023</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C273">
-        <v>5.49</v>
+        <v>8.99</v>
       </c>
       <c r="D273" t="s">
-        <v>286</v>
+        <v>31</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
-        <v>7894900501001</v>
+        <v>9002490229160</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>287</v>
       </c>
       <c r="C274">
-        <v>5.49</v>
+        <v>9.99</v>
       </c>
       <c r="D274" t="s">
-        <v>286</v>
+        <v>156</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
-        <v>7898275016023</v>
+        <v>9002490275013</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>288</v>
       </c>
       <c r="C275">
-        <v>8.99</v>
+        <v>9.99</v>
       </c>
       <c r="D275" t="s">
-        <v>31</v>
+        <v>156</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
-        <v>9002490229160</v>
+        <v>9002490247379</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>289</v>
@@ -5377,12 +5368,12 @@
         <v>9.99</v>
       </c>
       <c r="D276" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
-        <v>9002490275013</v>
+        <v>9002490258825</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>290</v>
@@ -5391,12 +5382,12 @@
         <v>9.99</v>
       </c>
       <c r="D277" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
-        <v>9002490247379</v>
+        <v>611269101713</v>
       </c>
       <c r="B278" s="2" t="s">
         <v>291</v>
@@ -5405,12 +5396,12 @@
         <v>9.99</v>
       </c>
       <c r="D278" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
-        <v>9002490258825</v>
+        <v>9002490283063</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>292</v>
@@ -5419,12 +5410,12 @@
         <v>9.99</v>
       </c>
       <c r="D279" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
-        <v>611269101713</v>
+        <v>611269991000</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>293</v>
@@ -5433,124 +5424,124 @@
         <v>9.99</v>
       </c>
       <c r="D280" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
-        <v>9002490283063</v>
+        <v>9002490243678</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>294</v>
       </c>
       <c r="C281">
-        <v>9.99</v>
+        <v>13.99</v>
       </c>
       <c r="D281" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
-        <v>611269991000</v>
+        <v>9002490209346</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>295</v>
       </c>
       <c r="C282">
-        <v>9.99</v>
+        <v>13.99</v>
       </c>
       <c r="D282" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
-        <v>9002490243678</v>
+        <v>9002490214166</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>296</v>
       </c>
       <c r="C283">
-        <v>13.99</v>
+        <v>17.989999999999998</v>
       </c>
       <c r="D283" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
-        <v>9002490209346</v>
+        <v>7891149441204</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>297</v>
       </c>
       <c r="C284">
-        <v>13.99</v>
+        <v>5.19</v>
       </c>
       <c r="D284" t="s">
-        <v>157</v>
+        <v>109</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
-        <v>9002490214166</v>
+        <v>7891149440801</v>
       </c>
       <c r="B285" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C285">
-        <v>17.989999999999998</v>
+        <v>6.69</v>
       </c>
       <c r="D285" t="s">
-        <v>157</v>
+        <v>109</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
-        <v>7891149441204</v>
+        <v>1220000250055</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>299</v>
       </c>
       <c r="C286">
-        <v>5.19</v>
+        <v>10.99</v>
       </c>
       <c r="D286" t="s">
-        <v>110</v>
+        <v>156</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
-        <v>7891149440801</v>
+        <v>7892840808020</v>
       </c>
       <c r="B287" s="2" t="s">
         <v>300</v>
       </c>
       <c r="C287">
-        <v>6.69</v>
+        <v>5.99</v>
       </c>
       <c r="D287" t="s">
-        <v>110</v>
+        <v>284</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
-        <v>1220000250055</v>
+        <v>7892840808037</v>
       </c>
       <c r="B288" s="2" t="s">
         <v>301</v>
       </c>
       <c r="C288">
-        <v>10.99</v>
+        <v>5.99</v>
       </c>
       <c r="D288" t="s">
-        <v>157</v>
+        <v>284</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
-        <v>7892840808020</v>
+        <v>7892840808174</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>302</v>
@@ -5559,12 +5550,12 @@
         <v>5.99</v>
       </c>
       <c r="D289" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
-        <v>7892840808037</v>
+        <v>7892840808044</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>303</v>
@@ -5573,12 +5564,12 @@
         <v>5.99</v>
       </c>
       <c r="D290" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
-        <v>7892840808174</v>
+        <v>7892840808051</v>
       </c>
       <c r="B291" s="2" t="s">
         <v>304</v>
@@ -5587,60 +5578,60 @@
         <v>5.99</v>
       </c>
       <c r="D291" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
-        <v>7892840808044</v>
+        <v>7891050004406</v>
       </c>
       <c r="B292" s="2" t="s">
         <v>305</v>
       </c>
       <c r="C292">
-        <v>5.99</v>
+        <v>29.99</v>
       </c>
       <c r="D292" t="s">
-        <v>286</v>
+        <v>53</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
-        <v>7892840808051</v>
+        <v>7892840822309</v>
       </c>
       <c r="B293" s="2" t="s">
         <v>306</v>
       </c>
       <c r="C293">
-        <v>5.99</v>
+        <v>3.69</v>
       </c>
       <c r="D293" t="s">
-        <v>286</v>
+        <v>27</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
-        <v>7891050004406</v>
+        <v>7892840822859</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>307</v>
       </c>
       <c r="C294">
-        <v>29.99</v>
+        <v>1.99</v>
       </c>
       <c r="D294" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
-        <v>7892840822309</v>
+        <v>7892840823061</v>
       </c>
       <c r="B295" s="2" t="s">
         <v>308</v>
       </c>
       <c r="C295">
-        <v>3.69</v>
+        <v>3.49</v>
       </c>
       <c r="D295" t="s">
         <v>27</v>
@@ -5648,13 +5639,13 @@
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
-        <v>7892840822859</v>
+        <v>7892840823504</v>
       </c>
       <c r="B296" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C296">
-        <v>1.99</v>
+        <v>3.49</v>
       </c>
       <c r="D296" t="s">
         <v>27</v>
@@ -5662,13 +5653,13 @@
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
-        <v>7892840823061</v>
+        <v>7891091061789</v>
       </c>
       <c r="B297" s="2" t="s">
         <v>310</v>
       </c>
       <c r="C297">
-        <v>3.49</v>
+        <v>9.99</v>
       </c>
       <c r="D297" t="s">
         <v>27</v>
@@ -5676,13 +5667,13 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
-        <v>7892840823504</v>
+        <v>7891091061680</v>
       </c>
       <c r="B298" s="2" t="s">
         <v>311</v>
       </c>
       <c r="C298">
-        <v>3.49</v>
+        <v>3.99</v>
       </c>
       <c r="D298" t="s">
         <v>27</v>
@@ -5690,13 +5681,13 @@
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
-        <v>7891091061789</v>
+        <v>7891091061697</v>
       </c>
       <c r="B299" s="2" t="s">
         <v>312</v>
       </c>
       <c r="C299">
-        <v>9.99</v>
+        <v>3.99</v>
       </c>
       <c r="D299" t="s">
         <v>27</v>
@@ -5704,7 +5695,7 @@
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
-        <v>7891091061680</v>
+        <v>7891091061932</v>
       </c>
       <c r="B300" s="2" t="s">
         <v>313</v>
@@ -5718,7 +5709,7 @@
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
-        <v>7891091061697</v>
+        <v>7891091061628</v>
       </c>
       <c r="B301" s="2" t="s">
         <v>314</v>
@@ -5732,7 +5723,7 @@
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
-        <v>7891091061932</v>
+        <v>7891091061710</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>315</v>
@@ -5746,7 +5737,7 @@
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
-        <v>7891091061628</v>
+        <v>7891091061659</v>
       </c>
       <c r="B303" s="2" t="s">
         <v>316</v>
@@ -5760,7 +5751,7 @@
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
-        <v>7891091061710</v>
+        <v>7891091061291</v>
       </c>
       <c r="B304" s="2" t="s">
         <v>317</v>
@@ -5774,13 +5765,13 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
-        <v>7891091061659</v>
+        <v>7892840822477</v>
       </c>
       <c r="B305" s="2" t="s">
         <v>318</v>
       </c>
       <c r="C305">
-        <v>3.99</v>
+        <v>1.99</v>
       </c>
       <c r="D305" t="s">
         <v>27</v>
@@ -5788,13 +5779,13 @@
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
-        <v>7891091061291</v>
+        <v>7892840822521</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>319</v>
       </c>
       <c r="C306">
-        <v>3.99</v>
+        <v>1.99</v>
       </c>
       <c r="D306" t="s">
         <v>27</v>
@@ -5802,13 +5793,13 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
-        <v>7892840822477</v>
+        <v>7892840822637</v>
       </c>
       <c r="B307" s="2" t="s">
         <v>320</v>
       </c>
       <c r="C307">
-        <v>1.99</v>
+        <v>2.99</v>
       </c>
       <c r="D307" t="s">
         <v>27</v>
@@ -5816,13 +5807,13 @@
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
-        <v>7892840822521</v>
+        <v>7892840822644</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>321</v>
       </c>
       <c r="C308">
-        <v>1.99</v>
+        <v>2.99</v>
       </c>
       <c r="D308" t="s">
         <v>27</v>
@@ -5830,77 +5821,77 @@
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
-        <v>7892840822637</v>
+        <v>7894900325362</v>
       </c>
       <c r="B309" s="2" t="s">
         <v>322</v>
       </c>
       <c r="C309">
-        <v>2.99</v>
+        <v>3.29</v>
       </c>
       <c r="D309" t="s">
-        <v>27</v>
+        <v>109</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
-        <v>7892840822644</v>
+        <v>7894900184075</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>323</v>
       </c>
       <c r="C310">
-        <v>2.99</v>
+        <v>5.99</v>
       </c>
       <c r="D310" t="s">
-        <v>27</v>
+        <v>109</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
-        <v>782</v>
+        <v>7891149840878</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>324</v>
       </c>
       <c r="C311">
-        <v>7.99</v>
+        <v>6.69</v>
       </c>
       <c r="D311" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
-        <v>7894900325362</v>
+        <v>7891991301114</v>
       </c>
       <c r="B312" s="2" t="s">
         <v>325</v>
       </c>
       <c r="C312">
-        <v>3.29</v>
+        <v>8.19</v>
       </c>
       <c r="D312" t="s">
-        <v>110</v>
+        <v>20</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
-        <v>7894900184075</v>
+        <v>7891991301138</v>
       </c>
       <c r="B313" s="2" t="s">
         <v>326</v>
       </c>
       <c r="C313">
-        <v>5.99</v>
+        <v>8.19</v>
       </c>
       <c r="D313" t="s">
-        <v>110</v>
+        <v>20</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
-        <v>7891149840878</v>
+        <v>7891149105564</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>327</v>
@@ -5914,13 +5905,13 @@
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
-        <v>7891991301114</v>
+        <v>7891991306164</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>328</v>
       </c>
       <c r="C315">
-        <v>8.19</v>
+        <v>6.69</v>
       </c>
       <c r="D315" t="s">
         <v>20</v>
@@ -5928,13 +5919,13 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
-        <v>7891991301138</v>
+        <v>7891149200504</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>329</v>
       </c>
       <c r="C316">
-        <v>8.19</v>
+        <v>4.29</v>
       </c>
       <c r="D316" t="s">
         <v>20</v>
@@ -5942,13 +5933,13 @@
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
-        <v>7891149105564</v>
+        <v>7891149201006</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>330</v>
       </c>
       <c r="C317">
-        <v>6.69</v>
+        <v>5.79</v>
       </c>
       <c r="D317" t="s">
         <v>20</v>
@@ -5956,77 +5947,77 @@
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
-        <v>7891991306164</v>
+        <v>7891991001359</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>331</v>
       </c>
       <c r="C318">
-        <v>6.69</v>
+        <v>8.59</v>
       </c>
       <c r="D318" t="s">
-        <v>20</v>
+        <v>109</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
-        <v>7891149200504</v>
+        <v>7891991002578</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>332</v>
       </c>
       <c r="C319">
-        <v>4.29</v>
+        <v>5.19</v>
       </c>
       <c r="D319" t="s">
-        <v>20</v>
+        <v>109</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
-        <v>7891149201006</v>
+        <v>7891150077263</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>333</v>
       </c>
       <c r="C320">
-        <v>5.79</v>
+        <v>27.99</v>
       </c>
       <c r="D320" t="s">
-        <v>20</v>
+        <v>271</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
-        <v>7891991001359</v>
+        <v>7891150050235</v>
       </c>
       <c r="B321" s="2" t="s">
         <v>334</v>
       </c>
       <c r="C321">
-        <v>8.59</v>
+        <v>27.99</v>
       </c>
       <c r="D321" t="s">
-        <v>110</v>
+        <v>271</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
-        <v>7891991002578</v>
+        <v>7891150050242</v>
       </c>
       <c r="B322" s="2" t="s">
         <v>335</v>
       </c>
       <c r="C322">
-        <v>5.19</v>
+        <v>27.99</v>
       </c>
       <c r="D322" t="s">
-        <v>110</v>
+        <v>271</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
-        <v>7891150077263</v>
+        <v>7891150055858</v>
       </c>
       <c r="B323" s="2" t="s">
         <v>336</v>
@@ -6035,172 +6026,172 @@
         <v>27.99</v>
       </c>
       <c r="D323" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
-        <v>7891150050235</v>
+        <v>7894900681260</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>337</v>
       </c>
       <c r="C324">
-        <v>27.99</v>
+        <v>5.79</v>
       </c>
       <c r="D324" t="s">
-        <v>273</v>
+        <v>109</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
-        <v>7891150050242</v>
+        <v>3003</v>
       </c>
       <c r="B325" s="2" t="s">
         <v>338</v>
       </c>
       <c r="C325">
-        <v>27.99</v>
+        <v>3.29</v>
       </c>
       <c r="D325" t="s">
-        <v>273</v>
+        <v>109</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" s="1">
-        <v>7891150055858</v>
+        <v>7894900061512</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>339</v>
       </c>
       <c r="C326">
-        <v>27.99</v>
+        <v>8.49</v>
       </c>
       <c r="D326" t="s">
-        <v>273</v>
+        <v>109</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
-        <v>7894900681260</v>
+        <v>7894900681017</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>340</v>
       </c>
       <c r="C327">
-        <v>5.79</v>
+        <v>2.99</v>
       </c>
       <c r="D327" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
-        <v>3003</v>
+        <v>7894900060010</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>341</v>
       </c>
       <c r="C328">
-        <v>3.29</v>
+        <v>2.79</v>
       </c>
       <c r="D328" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
-        <v>7894900061512</v>
+        <v>7894900681000</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>342</v>
       </c>
       <c r="C329">
-        <v>8.49</v>
+        <v>8.99</v>
       </c>
       <c r="D329" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
-        <v>7894900681017</v>
+        <v>7894900681178</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>343</v>
       </c>
       <c r="C330">
-        <v>2.99</v>
+        <v>2.19</v>
       </c>
       <c r="D330" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" s="1">
-        <v>7894900060010</v>
+        <v>78939738</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>344</v>
       </c>
       <c r="C331">
-        <v>2.79</v>
+        <v>1.99</v>
       </c>
       <c r="D331" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
-        <v>7894900681000</v>
+        <v>7898942775314</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>345</v>
       </c>
       <c r="C332">
-        <v>8.99</v>
+        <v>15.99</v>
       </c>
       <c r="D332" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
-        <v>7894900681178</v>
+        <v>7896945400813</v>
       </c>
       <c r="B333" s="2" t="s">
         <v>346</v>
       </c>
       <c r="C333">
-        <v>2.19</v>
+        <v>7.99</v>
       </c>
       <c r="D333" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
-        <v>78939738</v>
+        <v>78945494</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>347</v>
       </c>
       <c r="C334">
-        <v>1.99</v>
+        <v>2.99</v>
       </c>
       <c r="D334" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
-        <v>7898942775314</v>
+        <v>7894321722016</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>348</v>
       </c>
       <c r="C335">
-        <v>15.99</v>
+        <v>2.69</v>
       </c>
       <c r="D335" t="s">
         <v>31</v>
@@ -6208,13 +6199,13 @@
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
-        <v>7896945400813</v>
+        <v>7891137000055</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>349</v>
       </c>
       <c r="C336">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
       <c r="D336" t="s">
         <v>31</v>
@@ -6222,13 +6213,13 @@
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
-        <v>78945494</v>
+        <v>7891137006637</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>350</v>
       </c>
       <c r="C337">
-        <v>2.99</v>
+        <v>14.99</v>
       </c>
       <c r="D337" t="s">
         <v>31</v>
@@ -6236,13 +6227,13 @@
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
-        <v>7894321722016</v>
+        <v>7891137006620</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>351</v>
       </c>
       <c r="C338">
-        <v>2.69</v>
+        <v>7.99</v>
       </c>
       <c r="D338" t="s">
         <v>31</v>
@@ -6250,13 +6241,13 @@
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
-        <v>7891137000055</v>
+        <v>7891137000017</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>352</v>
       </c>
       <c r="C339">
-        <v>6.99</v>
+        <v>14.99</v>
       </c>
       <c r="D339" t="s">
         <v>31</v>
@@ -6264,13 +6255,13 @@
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
-        <v>7891137006637</v>
+        <v>78915398</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>353</v>
       </c>
       <c r="C340">
-        <v>14.99</v>
+        <v>7.99</v>
       </c>
       <c r="D340" t="s">
         <v>31</v>
@@ -6278,212 +6269,170 @@
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
-        <v>7891137006620</v>
+        <v>5604424244108</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>354</v>
       </c>
       <c r="C341">
-        <v>7.99</v>
+        <v>54.99</v>
       </c>
       <c r="D341" t="s">
-        <v>31</v>
+        <v>177</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
-        <v>7891137000017</v>
+        <v>7896037913146</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>355</v>
       </c>
       <c r="C342">
-        <v>14.99</v>
+        <v>16.989999999999998</v>
       </c>
       <c r="D342" t="s">
-        <v>31</v>
+        <v>177</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
-        <v>78915398</v>
+        <v>7312040017034</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>356</v>
       </c>
       <c r="C343">
-        <v>7.99</v>
+        <v>109.99</v>
       </c>
       <c r="D343" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
-        <v>5604424244108</v>
+        <v>7891050000903</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>357</v>
       </c>
       <c r="C344">
-        <v>54.99</v>
+        <v>37.99</v>
       </c>
       <c r="D344" t="s">
-        <v>178</v>
+        <v>53</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
-        <v>7896037913146</v>
+        <v>7898012860537</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>358</v>
       </c>
       <c r="C345">
-        <v>16.989999999999998</v>
+        <v>17.989999999999998</v>
       </c>
       <c r="D345" t="s">
-        <v>178</v>
+        <v>53</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" s="1">
-        <v>7312040017034</v>
+        <v>7893218003610</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>359</v>
       </c>
       <c r="C346">
-        <v>109.99</v>
+        <v>5.99</v>
       </c>
       <c r="D346" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" s="1">
-        <v>7891050000903</v>
+        <v>7893218003603</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>360</v>
       </c>
       <c r="C347">
-        <v>37.99</v>
+        <v>6.99</v>
       </c>
       <c r="D347" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" s="1">
-        <v>7898012860537</v>
+        <v>7893218000473</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>361</v>
       </c>
       <c r="C348">
-        <v>17.989999999999998</v>
+        <v>39.99</v>
       </c>
       <c r="D348" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
-        <v>7893218003610</v>
+        <v>50196081</v>
       </c>
       <c r="B349" s="2" t="s">
         <v>362</v>
       </c>
       <c r="C349">
-        <v>5.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="D349" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
-        <v>7893218003603</v>
+        <v>82184000328</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>363</v>
       </c>
       <c r="C350">
-        <v>6.99</v>
+        <v>149.99</v>
       </c>
       <c r="D350" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" s="1">
-        <v>7893218000473</v>
+        <v>5000281004020</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>364</v>
       </c>
       <c r="C351">
-        <v>39.99</v>
+        <v>149.99</v>
       </c>
       <c r="D351" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" s="1">
-        <v>50196081</v>
+        <v>5010106111956</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>365</v>
       </c>
       <c r="C352">
-        <v>69.989999999999995</v>
+        <v>99.99</v>
       </c>
       <c r="D352" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A353" s="1">
-        <v>82184000328</v>
-      </c>
-      <c r="B353" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="C353">
-        <v>149.99</v>
-      </c>
-      <c r="D353" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A354" s="1">
-        <v>5000281004020</v>
-      </c>
-      <c r="B354" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="C354">
-        <v>149.99</v>
-      </c>
-      <c r="D354" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A355" s="1">
-        <v>5010106111956</v>
-      </c>
-      <c r="B355" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="C355">
-        <v>99.99</v>
-      </c>
-      <c r="D355" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
